--- a/資料/説明(パッシブ・スキル)/黒い砂漠M_説明_MG.xlsx
+++ b/資料/説明(パッシブ・スキル)/黒い砂漠M_説明_MG.xlsx
@@ -2,27 +2,28 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(①)" sheetId="1" r:id="Rbc30308073d14365"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(②)" sheetId="2" r:id="Rd5133a2d7f374db1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(０)" sheetId="3" r:id="R286c0da935dc4ae9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(1)" sheetId="4" r:id="R4588d082b1204692"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(2)" sheetId="5" r:id="R37cddbc363bc47ac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(3)" sheetId="6" r:id="R0d3ae42d501348b7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(4)" sheetId="7" r:id="R35dad3e94aa941c4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(5)" sheetId="8" r:id="Rce2fdb5eb47f480c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(6)" sheetId="9" r:id="R4973a91d136f41f0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(7)" sheetId="10" r:id="Ra785f2733ab44065"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(8)" sheetId="11" r:id="R432a8302a7014c01"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(9)" sheetId="12" r:id="R83673eabe22a4373"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(10)" sheetId="13" r:id="R49554ae651a54110"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(11)" sheetId="14" r:id="R24c59e01e58d490e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(12)" sheetId="15" r:id="R78aae63a65f6468f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(13)" sheetId="16" r:id="R181257e629d74bfa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(1)" sheetId="17" r:id="R3c03ef798d4c46a2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(2)" sheetId="18" r:id="R2d0b56952f934f20"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(3)" sheetId="19" r:id="Rf1d90db20d544df7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(4)" sheetId="20" r:id="R3e2e09f7762946ec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(黒精霊の怒り)" sheetId="21" r:id="Rda058330d66a444a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(①)" sheetId="1" r:id="R7fc15839b0454006"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(②)" sheetId="2" r:id="R61e2159d81f04efa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(０)" sheetId="3" r:id="R2399d04164f84d5b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(1)" sheetId="4" r:id="Rab1cfed03f0b4ee2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(2)" sheetId="5" r:id="R8de5f3cbf9244c8e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(3)" sheetId="6" r:id="Re4a18cf951744fde"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(4)" sheetId="7" r:id="R1fec8018d826458c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(5)" sheetId="8" r:id="R93d9c07648b64718"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(6)" sheetId="9" r:id="R16f2b162077c426d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(7)" sheetId="10" r:id="R351810d364474a31"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(8)" sheetId="11" r:id="R5406c922eb5f44c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(9)" sheetId="12" r:id="R8bf1ea4b1e52459f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(10)" sheetId="13" r:id="R01b9d5e7b2e74638"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(11)" sheetId="14" r:id="Rb3ca398da4fd45bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(12)" sheetId="15" r:id="Rd280d51489fd4129"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(13)" sheetId="16" r:id="Rf4fa711cad634e69"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(1)" sheetId="17" r:id="R864000e7a3c74138"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(2)" sheetId="18" r:id="Rd422faebfb8c43d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(3)" sheetId="19" r:id="Ra6fb7a8a6b9f4d75"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(4)" sheetId="20" r:id="Rc66cd36511fd4139"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(黒精霊の怒り)" sheetId="21" r:id="R3248860c16934bc0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="プロフィール" sheetId="22" r:id="Rb4da4aed7a834f0d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3189,6 +3190,41 @@
 </x:worksheet>
 </file>
 
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="13.75" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="51.25" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="19.5" customHeight="1">
+      <x:c r="A1" t="str">
+        <x:v>名前</x:v>
+      </x:c>
+      <x:c r="B1" t="str">
+        <x:v>高銀(コ・ウン)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="19.5" customHeight="1">
+      <x:c r="A2" t="str">
+        <x:v>出身地</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:v>朝の国・左道房</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="19.5" customHeight="1">
+      <x:c r="A3" t="str">
+        <x:v>Other</x:v>
+      </x:c>
+      <x:c r="B3"/>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>

--- a/資料/説明(パッシブ・スキル)/黒い砂漠M_説明_MG.xlsx
+++ b/資料/説明(パッシブ・スキル)/黒い砂漠M_説明_MG.xlsx
@@ -2,28 +2,28 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(①)" sheetId="1" r:id="R7fc15839b0454006"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(②)" sheetId="2" r:id="R61e2159d81f04efa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(０)" sheetId="3" r:id="R2399d04164f84d5b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(1)" sheetId="4" r:id="Rab1cfed03f0b4ee2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(2)" sheetId="5" r:id="R8de5f3cbf9244c8e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(3)" sheetId="6" r:id="Re4a18cf951744fde"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(4)" sheetId="7" r:id="R1fec8018d826458c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(5)" sheetId="8" r:id="R93d9c07648b64718"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(6)" sheetId="9" r:id="R16f2b162077c426d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(7)" sheetId="10" r:id="R351810d364474a31"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(8)" sheetId="11" r:id="R5406c922eb5f44c8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(9)" sheetId="12" r:id="R8bf1ea4b1e52459f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(10)" sheetId="13" r:id="R01b9d5e7b2e74638"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(11)" sheetId="14" r:id="Rb3ca398da4fd45bb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(12)" sheetId="15" r:id="Rd280d51489fd4129"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(13)" sheetId="16" r:id="Rf4fa711cad634e69"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(1)" sheetId="17" r:id="R864000e7a3c74138"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(2)" sheetId="18" r:id="Rd422faebfb8c43d4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(3)" sheetId="19" r:id="Ra6fb7a8a6b9f4d75"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(4)" sheetId="20" r:id="Rc66cd36511fd4139"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(黒精霊の怒り)" sheetId="21" r:id="R3248860c16934bc0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="プロフィール" sheetId="22" r:id="Rb4da4aed7a834f0d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(①)" sheetId="1" r:id="R9ce2760edcf540e0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(②)" sheetId="2" r:id="R6d6af61a855f4cee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(０)" sheetId="3" r:id="R743ef6730d414a34"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(1)" sheetId="4" r:id="Rc7f2514afe8c4999"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(2)" sheetId="5" r:id="R9cab76adfbd344d5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(3)" sheetId="6" r:id="Rb366b1ce5fce481a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(4)" sheetId="7" r:id="Ra56ba987d1f14479"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(5)" sheetId="8" r:id="R9fd9cc6dd4d34464"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(6)" sheetId="9" r:id="R6bdb36bb6d51474c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(7)" sheetId="10" r:id="Rdc5a78c6c4e74905"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(8)" sheetId="11" r:id="Recb28bc34c434a5c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(9)" sheetId="12" r:id="Rf403567c61ab4116"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(10)" sheetId="13" r:id="R6346a9909c7743a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(11)" sheetId="14" r:id="Ra97093ba06134b2b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(12)" sheetId="15" r:id="Rdda76344d9fa4ad3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(13)" sheetId="16" r:id="R2356614c363c42d2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(1)" sheetId="17" r:id="Rff8ba5297e7847bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(2)" sheetId="18" r:id="Rbc4f363a48784f18"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(3)" sheetId="19" r:id="R0ea58dedbb7e454f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(4)" sheetId="20" r:id="R65267c718de344ff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(黒精霊の怒り)" sheetId="21" r:id="R9ad59b53597749cf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="プロフィール" sheetId="22" r:id="Red91ab9de9574921"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -654,7 +654,7 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="4" t="str"/>
+      <x:c r="A1" s="4"/>
       <x:c r="B1" s="4" t="str">
         <x:v>韓国語</x:v>
       </x:c>
@@ -699,11 +699,11 @@
         <x:v>PvP ｜系列 無欠 鮮明 かすかな</x:v>
       </x:c>
       <x:c r="E3" s="6" t="str">
-        <x:v>PvP ｜系列 無欠 鮮明 かすかな</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="30" customHeight="1">
-      <x:c r="A4" s="8" t="str"/>
+        <x:v>PvP</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="15" hidden="0" customHeight="1">
+      <x:c r="A4" s="8"/>
       <x:c r="B4" s="6" t="str">
         <x:v>"령부를 날린 후 순간적으로 이동한다."</x:v>
       </x:c>
@@ -714,11 +714,11 @@
         <x:v>「護符を飛ばした後、瞬時に移動します。」</x:v>
       </x:c>
       <x:c r="E4" s="6" t="str">
-        <x:v>「護符を飛ばした後、瞬時に移動します。」</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="30" customHeight="1">
-      <x:c r="A5" s="8" t="str"/>
+        <x:v>霊符を投げた後、瞬時に移動する。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="8"/>
       <x:c r="B5" s="6" t="str">
         <x:v>・최대 사용 횟수 : 1</x:v>
       </x:c>
@@ -729,11 +729,11 @@
         <x:v>・最大使用回数: 1</x:v>
       </x:c>
       <x:c r="E5" s="6" t="str">
-        <x:v>・最大使用回数: 1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="30" customHeight="1">
-      <x:c r="A6" s="8" t="str"/>
+        <x:v>最大使用回数：1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="8"/>
       <x:c r="B6" s="6" t="str">
         <x:v>・재사용 대기시간 : 10초</x:v>
       </x:c>
@@ -744,97 +744,115 @@
         <x:v>・再使用待機時間: 10秒</x:v>
       </x:c>
       <x:c r="E6" s="6" t="str">
-        <x:v>・再使用待機時間: 10秒</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="30" customHeight="1">
-      <x:c r="A7" s="8" t="str"/>
-      <x:c r="B7" s="6" t="str">
+        <x:v>再使用待機時間：10秒</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="8"/>
+      <x:c r="B7" s="6"/>
+      <x:c r="C7" s="6"/>
+      <x:c r="D7" s="6"/>
+      <x:c r="E7" s="6" t="str">
+        <x:v>・打撃ダメージ1936.59%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="8"/>
+      <x:c r="B8" s="6"/>
+      <x:c r="C8" s="6"/>
+      <x:c r="D8" s="6"/>
+      <x:c r="E8" s="6" t="str">
+        <x:v>・PVP打撃ダメージ968.29%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="8"/>
+      <x:c r="B9" s="6" t="str">
         <x:v>・기술 버튼 유지 시 최대 2 타격</x:v>
       </x:c>
-      <x:c r="C7" s="6" t="str">
+      <x:c r="C9" s="6" t="str">
         <x:v>・Max 2 hits when holding skill button</x:v>
       </x:c>
-      <x:c r="D7" s="6" t="str">
+      <x:c r="D9" s="6" t="str">
         <x:v>・技術ボタン押しっぱなしで最大2ヒット</x:v>
       </x:c>
-      <x:c r="E7" s="6" t="str">
-        <x:v>・技術ボタン押しっぱなしで最大2ヒット</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="30" customHeight="1">
-      <x:c r="A8" s="8" t="str"/>
-      <x:c r="B8" s="6" t="str">
+      <x:c r="E9" s="6" t="str">
+        <x:v>・スキルボタン長押しで最大2打撃</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" s="8"/>
+      <x:c r="B10" s="6" t="str">
         <x:v>・이동 중 슈퍼 아머 , 피해 감소 , 잡기 불가</x:v>
       </x:c>
-      <x:c r="C8" s="6" t="str">
+      <x:c r="C10" s="6" t="str">
         <x:v>・While moving Super Armor , Damage Reduction , Grab Immunity</x:v>
       </x:c>
-      <x:c r="D8" s="6" t="str">
+      <x:c r="D10" s="6" t="str">
         <x:v>・移動中スーパーアーマー、被害減少、掴み無効</x:v>
       </x:c>
-      <x:c r="E8" s="6" t="str">
-        <x:v>・移動中スーパーアーマー、被害減少、掴み無効</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="30" customHeight="1">
-      <x:c r="A9" s="8" t="str"/>
-      <x:c r="B9" s="6" t="str">
+      <x:c r="E10" s="6" t="str">
+        <x:v>・移動中、スーパーアーマー、ダメージ減少、キャッチ不可</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11" s="8"/>
+      <x:c r="B11" s="6" t="str">
         <x:v>・공격 중 슈퍼 아머 , 잡기 불가</x:v>
       </x:c>
-      <x:c r="C9" s="6" t="str">
+      <x:c r="C11" s="6" t="str">
         <x:v>・While attacking Super Armor , Grab Immunity</x:v>
       </x:c>
-      <x:c r="D9" s="6" t="str">
+      <x:c r="D11" s="6" t="str">
         <x:v>・スーパーアーマー攻撃中、免疫獲得</x:v>
       </x:c>
-      <x:c r="E9" s="6" t="str">
-        <x:v>・スーパーアーマー攻撃中、免疫獲得</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="30" customHeight="1">
-      <x:c r="A10" s="8" t="str"/>
-      <x:c r="B10" s="6" t="str">
+      <x:c r="E11" s="6" t="str">
+        <x:v>・攻撃中、スーパーアーマー、キャッチ不可</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
+      <x:c r="A12" s="8"/>
+      <x:c r="B12" s="6" t="str">
         <x:v>・착지 시 슈퍼 아머</x:v>
       </x:c>
-      <x:c r="C10" s="6" t="str">
+      <x:c r="C12" s="6" t="str">
         <x:v>・Upon landing Super Armor</x:v>
       </x:c>
-      <x:c r="D10" s="6" t="str">
+      <x:c r="D12" s="6" t="str">
         <x:v>・スーパーアーマー着地時</x:v>
       </x:c>
-      <x:c r="E10" s="6" t="str">
-        <x:v>・スーパーアーマー着地時</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="30" customHeight="1">
-      <x:c r="A11" s="8" t="str"/>
-      <x:c r="B11" s="6" t="str">
+      <x:c r="E12" s="6" t="str">
+        <x:v>・着地時、スーパーアーマー</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="15" hidden="0" customHeight="1">
+      <x:c r="A13" s="5"/>
+      <x:c r="B13" s="5" t="str">
         <x:v>・타격 성공 시 바운드</x:v>
       </x:c>
-      <x:c r="C11" s="6" t="str">
+      <x:c r="C13" s="5" t="str">
         <x:v>・On successful hit Bound</x:v>
       </x:c>
-      <x:c r="D11" s="6" t="str">
+      <x:c r="D13" s="5" t="str">
         <x:v>・ヒット成功時 バウンド</x:v>
       </x:c>
-      <x:c r="E11" s="6" t="str">
-        <x:v>・ヒット成功時 バウンド</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="30" customHeight="1">
-      <x:c r="A12" s="8" t="str"/>
-      <x:c r="B12" s="6" t="str">
+      <x:c r="E13" s="5" t="str">
+        <x:v>・打撃成功時、バウンド</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="15" hidden="0" customHeight="1">
+      <x:c r="A14" s="5"/>
+      <x:c r="B14" s="5" t="str">
         <x:v>・기술 버튼 유지 시 대상에게 순간이동</x:v>
       </x:c>
-      <x:c r="C12" s="6" t="str">
+      <x:c r="C14" s="5" t="str">
         <x:v>・Teleport to target when holding skill button</x:v>
       </x:c>
-      <x:c r="D12" s="6" t="str">
+      <x:c r="D14" s="5" t="str">
         <x:v>・技術ボタンを押し続けるとターゲットにテレポートします</x:v>
       </x:c>
-      <x:c r="E12" s="6" t="str">
-        <x:v>・技術ボタンを押し続けるとターゲットにテレポートします</x:v>
+      <x:c r="E14" s="5" t="str">
+        <x:v>・スキルボタン長押しで対象の位置に瞬間移動</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -854,7 +872,7 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="4" t="str"/>
+      <x:c r="A1" s="4"/>
       <x:c r="B1" s="4" t="str">
         <x:v>韓国語</x:v>
       </x:c>
@@ -882,7 +900,7 @@
         <x:v>狐走り</x:v>
       </x:c>
       <x:c r="E2" s="6" t="str">
-        <x:v>狐走り</x:v>
+        <x:v>狐駆け</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="30" customHeight="1">
@@ -899,11 +917,11 @@
         <x:v>PvE PvP ｜系列 無欠 鮮明 かすかな</x:v>
       </x:c>
       <x:c r="E3" s="6" t="str">
-        <x:v>PvE PvP ｜系列 無欠 鮮明 かすかな</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="30" customHeight="1">
-      <x:c r="A4" s="8" t="str"/>
+        <x:v>PvE PvP</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A4" s="8"/>
       <x:c r="B4" s="6" t="str">
         <x:v>"여우불로 몸을 감싸 모습을 감추며 돌진한다. 흩날리는 여우불은 주변의 적들에게 불타는 고통을 선사한다."</x:v>
       </x:c>
@@ -914,11 +932,12 @@
         <x:v>「フォックスファイヤーで身を隠しながらダッシュする。羽ばたくフォックスファイヤーは周囲の敵に灼熱の苦痛を与える。」</x:v>
       </x:c>
       <x:c r="E4" s="6" t="str">
-        <x:v>「フォックスファイヤーで身を隠しながらダッシュする。羽ばたくフォックスファイヤーは周囲の敵に灼熱の苦痛を与える。」</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="30" customHeight="1">
-      <x:c r="A5" s="8" t="str"/>
+        <x:v>狐火で全身を包み込み、姿を隠して前方へ突進する。
+舞い散った狐火は、周囲の敵に燃えるような痛みを与える。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="8"/>
       <x:c r="B5" s="6" t="str">
         <x:v>・최대 사용 횟수 : 1</x:v>
       </x:c>
@@ -929,11 +948,11 @@
         <x:v>・最大使用回数: 1</x:v>
       </x:c>
       <x:c r="E5" s="6" t="str">
-        <x:v>・最大使用回数: 1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="30" customHeight="1">
-      <x:c r="A6" s="8" t="str"/>
+        <x:v>最大使用回数：1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="8"/>
       <x:c r="B6" s="6" t="str">
         <x:v>・재사용 대기시간 : 10초</x:v>
       </x:c>
@@ -944,127 +963,145 @@
         <x:v>・再使用待機時間: 10秒</x:v>
       </x:c>
       <x:c r="E6" s="6" t="str">
-        <x:v>・再使用待機時間: 10秒</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="30" customHeight="1">
-      <x:c r="A7" s="8" t="str"/>
-      <x:c r="B7" s="6" t="str">
+        <x:v>再使用待機時間：10秒</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="8"/>
+      <x:c r="B7" s="6"/>
+      <x:c r="C7" s="6"/>
+      <x:c r="D7" s="6"/>
+      <x:c r="E7" s="6" t="str">
+        <x:v>・打撃ダメージ481.58%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="8"/>
+      <x:c r="B8" s="6"/>
+      <x:c r="C8" s="6"/>
+      <x:c r="D8" s="6"/>
+      <x:c r="E8" s="6" t="str">
+        <x:v>・PVP打撃ダメージ240.79%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="8"/>
+      <x:c r="B9" s="6" t="str">
         <x:v>・최대 3 타격</x:v>
       </x:c>
-      <x:c r="C7" s="6" t="str">
+      <x:c r="C9" s="6" t="str">
         <x:v>・Max 3 hits</x:v>
       </x:c>
-      <x:c r="D7" s="6" t="str">
+      <x:c r="D9" s="6" t="str">
         <x:v>・最大3ヒット</x:v>
       </x:c>
-      <x:c r="E7" s="6" t="str">
-        <x:v>・最大3ヒット</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="30" customHeight="1">
-      <x:c r="A8" s="8" t="str"/>
-      <x:c r="B8" s="6" t="str">
+      <x:c r="E9" s="6" t="str">
+        <x:v>・最大3打撃</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A10" s="8"/>
+      <x:c r="B10" s="6" t="str">
         <x:v>・기술 버튼 유지 시 정신력 40 을 소모하여 최대 2 회 추가 이동</x:v>
       </x:c>
-      <x:c r="C8" s="6" t="str">
+      <x:c r="C10" s="6" t="str">
         <x:v>・Consumes 40 MP to perform max 2 additional movements when holding skill button</x:v>
       </x:c>
-      <x:c r="D8" s="6" t="str">
+      <x:c r="D10" s="6" t="str">
         <x:v>・技術ボタンを押している間、40 精神力を消費して最大2つの追加動作を実行します</x:v>
       </x:c>
-      <x:c r="E8" s="6" t="str">
-        <x:v>・技術ボタンを押している間、40 精神力を消費して最大2つの追加動作を実行します</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="30" customHeight="1">
-      <x:c r="A9" s="8" t="str"/>
-      <x:c r="B9" s="6" t="str">
+      <x:c r="E10" s="6" t="str">
+        <x:v>・スキルボタン長押しでMPを40消費し最大2回追加移動可能</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11" s="8"/>
+      <x:c r="B11" s="6" t="str">
         <x:v>・즉시 발동 기술</x:v>
       </x:c>
-      <x:c r="C9" s="6" t="str">
+      <x:c r="C11" s="6" t="str">
         <x:v>・Instant Activation Skill</x:v>
       </x:c>
-      <x:c r="D9" s="6" t="str">
+      <x:c r="D11" s="6" t="str">
         <x:v>・即時発動技術</x:v>
       </x:c>
-      <x:c r="E9" s="6" t="str">
-        <x:v>・即時発動技術</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="30" customHeight="1">
-      <x:c r="A10" s="8" t="str"/>
-      <x:c r="B10" s="6" t="str">
+      <x:c r="E11" s="6" t="str">
+        <x:v>・即時発動スキル</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
+      <x:c r="A12" s="8"/>
+      <x:c r="B12" s="6" t="str">
         <x:v>・이동 중 슈퍼 아머 , 피해 감소</x:v>
       </x:c>
-      <x:c r="C10" s="6" t="str">
+      <x:c r="C12" s="6" t="str">
         <x:v>・While moving Super Armor , Damage Reduction</x:v>
       </x:c>
-      <x:c r="D10" s="6" t="str">
+      <x:c r="D12" s="6" t="str">
         <x:v>・スーパーアーマー移動中、被害減少</x:v>
       </x:c>
-      <x:c r="E10" s="6" t="str">
-        <x:v>・スーパーアーマー移動中、被害減少</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="30" customHeight="1">
-      <x:c r="A11" s="8" t="str"/>
-      <x:c r="B11" s="6" t="str">
+      <x:c r="E12" s="6" t="str">
+        <x:v>・移動中、スーパーアーマー、ダメージ減少</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="15" hidden="0" customHeight="1">
+      <x:c r="A13" s="8"/>
+      <x:c r="B13" s="6" t="str">
         <x:v>・공격 중 슈퍼 아머</x:v>
       </x:c>
-      <x:c r="C11" s="6" t="str">
+      <x:c r="C13" s="6" t="str">
         <x:v>・While attacking Super Armor</x:v>
       </x:c>
-      <x:c r="D11" s="6" t="str">
+      <x:c r="D13" s="6" t="str">
         <x:v>・スーパーアーマー攻撃時</x:v>
       </x:c>
-      <x:c r="E11" s="6" t="str">
-        <x:v>・スーパーアーマー攻撃時</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="30" customHeight="1">
-      <x:c r="A12" s="8" t="str"/>
-      <x:c r="B12" s="6" t="str">
+      <x:c r="E13" s="6" t="str">
+        <x:v>・攻撃中、スーパーアーマー</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="15" hidden="0" customHeight="1">
+      <x:c r="A14" s="8"/>
+      <x:c r="B14" s="6" t="str">
         <x:v>・마지막 타격 성공 시 경직</x:v>
       </x:c>
-      <x:c r="C12" s="6" t="str">
+      <x:c r="C14" s="6" t="str">
         <x:v>・On last successful hit Stiffness</x:v>
       </x:c>
-      <x:c r="D12" s="6" t="str">
+      <x:c r="D14" s="6" t="str">
         <x:v>・最後に成功したヒット時の剛性</x:v>
       </x:c>
-      <x:c r="E12" s="6" t="str">
-        <x:v>・最後に成功したヒット時の剛性</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="30" customHeight="1">
-      <x:c r="A13" s="8" t="str"/>
-      <x:c r="B13" s="6" t="str">
+      <x:c r="E14" s="6" t="str">
+        <x:v>・最後の打撃成功時、硬直</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="15" hidden="0" customHeight="1">
+      <x:c r="A15" s="5"/>
+      <x:c r="B15" s="5" t="str">
         <x:v>・추가 이동 시 신령의 기운 1 획득</x:v>
       </x:c>
-      <x:c r="C13" s="6" t="str">
+      <x:c r="C15" s="5" t="str">
         <x:v>・Acquire 1 Spirit Energy on additional movement</x:v>
       </x:c>
-      <x:c r="D13" s="6" t="str">
+      <x:c r="D15" s="5" t="str">
         <x:v>・追加移動で精霊エネルギーを1個獲得</x:v>
       </x:c>
-      <x:c r="E13" s="6" t="str">
-        <x:v>・追加移動で精霊エネルギーを1個獲得</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="30" customHeight="1">
-      <x:c r="A14" s="8" t="str"/>
-      <x:c r="B14" s="6" t="str">
+      <x:c r="E15" s="5" t="str">
+        <x:v>・追加移動時、神霊のオーラ1個獲得</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="15" hidden="0" customHeight="1">
+      <x:c r="A16" s="5"/>
+      <x:c r="B16" s="5" t="str">
         <x:v>・이동 시마다 여우불 3개 발사</x:v>
       </x:c>
-      <x:c r="C14" s="6" t="str">
+      <x:c r="C16" s="5" t="str">
         <x:v>・Fires 3 Fox Fires every time you move</x:v>
       </x:c>
-      <x:c r="D14" s="6" t="str">
+      <x:c r="D16" s="5" t="str">
         <x:v>・移動するたびにフォックスファイヤーを3発発射する</x:v>
       </x:c>
-      <x:c r="E14" s="6" t="str">
-        <x:v>・移動するたびにフォックスファイヤーを3発発射する</x:v>
+      <x:c r="E16" s="5" t="str">
+        <x:v>・移動時に狐火を3個放つ</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1084,7 +1121,7 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="4" t="str"/>
+      <x:c r="A1" s="4"/>
       <x:c r="B1" s="4" t="str">
         <x:v>韓国語</x:v>
       </x:c>
@@ -1129,11 +1166,11 @@
         <x:v>PvP ｜系列 無欠 鮮明 かすかな</x:v>
       </x:c>
       <x:c r="E3" s="6" t="str">
-        <x:v>PvP ｜系列 無欠 鮮明 かすかな</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="30" customHeight="1">
-      <x:c r="A4" s="8" t="str"/>
+        <x:v>PvP</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="15" hidden="0" customHeight="1">
+      <x:c r="A4" s="8"/>
       <x:c r="B4" s="6" t="str">
         <x:v>"빠르게 이동하며 령부를 날려 적을 공격한다."</x:v>
       </x:c>
@@ -1144,11 +1181,11 @@
         <x:v>「素早く移動しながら護符を飛ばして敵を攻撃します。」</x:v>
       </x:c>
       <x:c r="E4" s="6" t="str">
-        <x:v>「素早く移動しながら護符を飛ばして敵を攻撃します。」</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="30" customHeight="1">
-      <x:c r="A5" s="8" t="str"/>
+        <x:v>素早く移動しながら霊符を飛ばして敵を攻撃する。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="8"/>
       <x:c r="B5" s="6" t="str">
         <x:v>・최대 사용 횟수 : 4</x:v>
       </x:c>
@@ -1159,11 +1196,11 @@
         <x:v>・最大使用回数: 4</x:v>
       </x:c>
       <x:c r="E5" s="6" t="str">
-        <x:v>・最大使用回数: 4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="30" customHeight="1">
-      <x:c r="A6" s="8" t="str"/>
+        <x:v>最大使用回数：4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="8"/>
       <x:c r="B6" s="6" t="str">
         <x:v>・재사용 대기시간 : 4초</x:v>
       </x:c>
@@ -1174,82 +1211,100 @@
         <x:v>・再使用待機時間: 4秒</x:v>
       </x:c>
       <x:c r="E6" s="6" t="str">
-        <x:v>・再使用待機時間: 4秒</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="30" customHeight="1">
-      <x:c r="A7" s="8" t="str"/>
-      <x:c r="B7" s="6" t="str">
+        <x:v>再使用待機時間：4秒</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="8"/>
+      <x:c r="B7" s="6"/>
+      <x:c r="C7" s="6"/>
+      <x:c r="D7" s="6"/>
+      <x:c r="E7" s="6" t="str">
+        <x:v>・打撃ダメージ1220%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="8"/>
+      <x:c r="B8" s="6"/>
+      <x:c r="C8" s="6"/>
+      <x:c r="D8" s="6"/>
+      <x:c r="E8" s="6" t="str">
+        <x:v>・PVP打撃ダメージ610%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="8"/>
+      <x:c r="B9" s="6" t="str">
         <x:v>・기술 버튼 유지 시 최대 3 타격</x:v>
       </x:c>
-      <x:c r="C7" s="6" t="str">
+      <x:c r="C9" s="6" t="str">
         <x:v>・Max 3 hits when holding skill button</x:v>
       </x:c>
-      <x:c r="D7" s="6" t="str">
+      <x:c r="D9" s="6" t="str">
         <x:v>・技術ボタン押しっぱなしで最大3ヒット</x:v>
       </x:c>
-      <x:c r="E7" s="6" t="str">
-        <x:v>・技術ボタン押しっぱなしで最大3ヒット</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="30" customHeight="1">
-      <x:c r="A8" s="8" t="str"/>
-      <x:c r="B8" s="6" t="str">
+      <x:c r="E9" s="6" t="str">
+        <x:v>・スキルボタン長押しで最大3打撃</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" s="8"/>
+      <x:c r="B10" s="6" t="str">
         <x:v>・기술 사용 중 슈퍼 아머</x:v>
       </x:c>
-      <x:c r="C8" s="6" t="str">
+      <x:c r="C10" s="6" t="str">
         <x:v>・Super Armor during skill use</x:v>
       </x:c>
-      <x:c r="D8" s="6" t="str">
+      <x:c r="D10" s="6" t="str">
         <x:v>・技術使用時のスーパーアーマー</x:v>
       </x:c>
-      <x:c r="E8" s="6" t="str">
-        <x:v>・技術使用時のスーパーアーマー</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="30" customHeight="1">
-      <x:c r="A9" s="8" t="str"/>
-      <x:c r="B9" s="6" t="str">
+      <x:c r="E10" s="6" t="str">
+        <x:v>・スキル使用中、スーパーアーマー</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11" s="8"/>
+      <x:c r="B11" s="6" t="str">
         <x:v>・첫 타격 성공 시 경직</x:v>
       </x:c>
-      <x:c r="C9" s="6" t="str">
+      <x:c r="C11" s="6" t="str">
         <x:v>・On first successful hit Stiffness</x:v>
       </x:c>
-      <x:c r="D9" s="6" t="str">
+      <x:c r="D11" s="6" t="str">
         <x:v>・最初のヒット成功時の剛性</x:v>
       </x:c>
-      <x:c r="E9" s="6" t="str">
-        <x:v>・最初のヒット成功時の剛性</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="30" customHeight="1">
-      <x:c r="A10" s="8" t="str"/>
-      <x:c r="B10" s="6" t="str">
+      <x:c r="E11" s="6" t="str">
+        <x:v>・1回目の打撃成功時、硬直</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
+      <x:c r="A12" s="5"/>
+      <x:c r="B12" s="5" t="str">
         <x:v>・두 번째 타격 성공 시 기절</x:v>
       </x:c>
-      <x:c r="C10" s="6" t="str">
+      <x:c r="C12" s="5" t="str">
         <x:v>・On second successful hit Stun</x:v>
       </x:c>
-      <x:c r="D10" s="6" t="str">
+      <x:c r="D12" s="5" t="str">
         <x:v>・2回目のヒットでスタン</x:v>
       </x:c>
-      <x:c r="E10" s="6" t="str">
-        <x:v>・2回目のヒットでスタン</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="30" customHeight="1">
-      <x:c r="A11" s="8" t="str"/>
-      <x:c r="B11" s="6" t="str">
+      <x:c r="E12" s="5" t="str">
+        <x:v>・2回目の打撃成功時、気絶</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="15" hidden="0" customHeight="1">
+      <x:c r="A13" s="5"/>
+      <x:c r="B13" s="5" t="str">
         <x:v>・이동 공격 가능</x:v>
       </x:c>
-      <x:c r="C11" s="6" t="str">
+      <x:c r="C13" s="5" t="str">
         <x:v>・Possible to move while attacking</x:v>
       </x:c>
-      <x:c r="D11" s="6" t="str">
+      <x:c r="D13" s="5" t="str">
         <x:v>・攻撃しながら移動可能</x:v>
       </x:c>
-      <x:c r="E11" s="6" t="str">
-        <x:v>・攻撃しながら移動可能</x:v>
+      <x:c r="E13" s="5" t="str">
+        <x:v>・移動攻撃可能</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1269,7 +1324,7 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="4" t="str"/>
+      <x:c r="A1" s="4"/>
       <x:c r="B1" s="4" t="str">
         <x:v>韓国語</x:v>
       </x:c>
@@ -1297,7 +1352,7 @@
         <x:v>咲き上がり</x:v>
       </x:c>
       <x:c r="E2" s="6" t="str">
-        <x:v>咲き上がり</x:v>
+        <x:v>火織</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="30" customHeight="1">
@@ -1314,11 +1369,11 @@
         <x:v>PvP ｜系列 無欠 鮮明 洗練された</x:v>
       </x:c>
       <x:c r="E3" s="6" t="str">
-        <x:v>PvP ｜系列 無欠 鮮明 洗練された</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="30" customHeight="1">
-      <x:c r="A4" s="8" t="str"/>
+        <x:v>PvP</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A4" s="8"/>
       <x:c r="B4" s="6" t="str">
         <x:v>"흐르는 듯한 움직임으로 이동한 후 여우불로 전방의 적들을 짓누른다."</x:v>
       </x:c>
@@ -1329,11 +1384,11 @@
         <x:v>「流れるような動きで前方の敵をフォックスファイヤーで粉砕する」</x:v>
       </x:c>
       <x:c r="E4" s="6" t="str">
-        <x:v>「流れるような動きで前方の敵をフォックスファイヤーで粉砕する」</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="30" customHeight="1">
-      <x:c r="A5" s="8" t="str"/>
+        <x:v>流れるような動きで移動し、狐火の力で前方の敵を押し潰す。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="8"/>
       <x:c r="B5" s="6" t="str">
         <x:v>・최대 사용 횟수 : 2</x:v>
       </x:c>
@@ -1344,11 +1399,11 @@
         <x:v>・最大使用回数: 2</x:v>
       </x:c>
       <x:c r="E5" s="6" t="str">
-        <x:v>・最大使用回数: 2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="30" customHeight="1">
-      <x:c r="A6" s="8" t="str"/>
+        <x:v>最大使用回数：2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="8"/>
       <x:c r="B6" s="6" t="str">
         <x:v>・재사용 대기시간 : 7초</x:v>
       </x:c>
@@ -1359,82 +1414,100 @@
         <x:v>・再使用待機時間: 7秒</x:v>
       </x:c>
       <x:c r="E6" s="6" t="str">
-        <x:v>・再使用待機時間: 7秒</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="30" customHeight="1">
-      <x:c r="A7" s="8" t="str"/>
-      <x:c r="B7" s="6" t="str">
+        <x:v>再使用待機時間：7秒</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="8"/>
+      <x:c r="B7" s="6"/>
+      <x:c r="C7" s="6"/>
+      <x:c r="D7" s="6"/>
+      <x:c r="E7" s="6" t="str">
+        <x:v>・打撃ダメージ1194.32%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="8"/>
+      <x:c r="B8" s="6"/>
+      <x:c r="C8" s="6"/>
+      <x:c r="D8" s="6"/>
+      <x:c r="E8" s="6" t="str">
+        <x:v>・PVP打撃ダメージ597.16%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="8"/>
+      <x:c r="B9" s="6" t="str">
         <x:v>・기술 버튼 유지 시 최대 3 타격</x:v>
       </x:c>
-      <x:c r="C7" s="6" t="str">
+      <x:c r="C9" s="6" t="str">
         <x:v>・Max 3 hits when holding skill button</x:v>
       </x:c>
-      <x:c r="D7" s="6" t="str">
+      <x:c r="D9" s="6" t="str">
         <x:v>・技術ボタン押しっぱなしで最大3ヒット</x:v>
       </x:c>
-      <x:c r="E7" s="6" t="str">
-        <x:v>・技術ボタン押しっぱなしで最大3ヒット</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="30" customHeight="1">
-      <x:c r="A8" s="8" t="str"/>
-      <x:c r="B8" s="6" t="str">
+      <x:c r="E9" s="6" t="str">
+        <x:v>・スキルボタン長押しで最大4打撃</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" s="8"/>
+      <x:c r="B10" s="6" t="str">
         <x:v>・즉시 발동 기술</x:v>
       </x:c>
-      <x:c r="C8" s="6" t="str">
+      <x:c r="C10" s="6" t="str">
         <x:v>・Instant Activation Skill</x:v>
       </x:c>
-      <x:c r="D8" s="6" t="str">
+      <x:c r="D10" s="6" t="str">
         <x:v>・即時発動技術</x:v>
       </x:c>
-      <x:c r="E8" s="6" t="str">
-        <x:v>・即時発動技術</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="30" customHeight="1">
-      <x:c r="A9" s="8" t="str"/>
-      <x:c r="B9" s="6" t="str">
+      <x:c r="E10" s="6" t="str">
+        <x:v>・即時発動スキル</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11" s="8"/>
+      <x:c r="B11" s="6" t="str">
         <x:v>・이동 중 슈퍼 아머 , 피해 감소 , 잡기 불가</x:v>
       </x:c>
-      <x:c r="C9" s="6" t="str">
+      <x:c r="C11" s="6" t="str">
         <x:v>・While moving Super Armor , Damage Reduction , Grab Immunity</x:v>
       </x:c>
-      <x:c r="D9" s="6" t="str">
+      <x:c r="D11" s="6" t="str">
         <x:v>・移動中スーパーアーマー、被害減少、掴み無効</x:v>
       </x:c>
-      <x:c r="E9" s="6" t="str">
-        <x:v>・移動中スーパーアーマー、被害減少、掴み無効</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="30" customHeight="1">
-      <x:c r="A10" s="8" t="str"/>
-      <x:c r="B10" s="6" t="str">
+      <x:c r="E11" s="6" t="str">
+        <x:v>・移動中、スーパーアーマー、ダメージ減少、キャッチ不可</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
+      <x:c r="A12" s="5"/>
+      <x:c r="B12" s="5" t="str">
         <x:v>・공격 중 슈퍼 아머</x:v>
       </x:c>
-      <x:c r="C10" s="6" t="str">
+      <x:c r="C12" s="5" t="str">
         <x:v>・While attacking Super Armor</x:v>
       </x:c>
-      <x:c r="D10" s="6" t="str">
+      <x:c r="D12" s="5" t="str">
         <x:v>・スーパーアーマー攻撃時</x:v>
       </x:c>
-      <x:c r="E10" s="6" t="str">
-        <x:v>・スーパーアーマー攻撃時</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="30" customHeight="1">
-      <x:c r="A11" s="8" t="str"/>
-      <x:c r="B11" s="6" t="str">
+      <x:c r="E12" s="5" t="str">
+        <x:v>・攻撃中、スーパーアーマー</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="15" hidden="0" customHeight="1">
+      <x:c r="A13" s="5"/>
+      <x:c r="B13" s="5" t="str">
         <x:v>・마지막 타격 성공 시 바운드</x:v>
       </x:c>
-      <x:c r="C11" s="6" t="str">
+      <x:c r="C13" s="5" t="str">
         <x:v>・On last successful hit Bound</x:v>
       </x:c>
-      <x:c r="D11" s="6" t="str">
+      <x:c r="D13" s="5" t="str">
         <x:v>・最後に成功したヒット時</x:v>
       </x:c>
-      <x:c r="E11" s="6" t="str">
-        <x:v>・最後に成功したヒット時</x:v>
+      <x:c r="E13" s="5" t="str">
+        <x:v>・最後の打撃成功時、バウンド</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1454,7 +1527,7 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="4" t="str"/>
+      <x:c r="A1" s="4"/>
       <x:c r="B1" s="4" t="str">
         <x:v>韓国語</x:v>
       </x:c>
@@ -1499,11 +1572,11 @@
         <x:v>PvE ｜系列 守護 無欠 鮮明</x:v>
       </x:c>
       <x:c r="E3" s="6" t="str">
-        <x:v>PvE ｜系列 守護 無欠 鮮明</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="30" customHeight="1">
-      <x:c r="A4" s="8" t="str"/>
+        <x:v>PvE</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="15" hidden="0" customHeight="1">
+      <x:c r="A4" s="8"/>
       <x:c r="B4" s="6" t="str">
         <x:v>"령부를 불태워 자연을 조종한다."</x:v>
       </x:c>
@@ -1514,11 +1587,11 @@
         <x:v>「護符を燃やすことで自然を制御する。」</x:v>
       </x:c>
       <x:c r="E4" s="6" t="str">
-        <x:v>「護符を燃やすことで自然を制御する。」</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="30" customHeight="1">
-      <x:c r="A5" s="8" t="str"/>
+        <x:v>霊符を燃やして自然を操る。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="8"/>
       <x:c r="B5" s="6" t="str">
         <x:v>・최대 사용 횟수 : 1</x:v>
       </x:c>
@@ -1529,11 +1602,11 @@
         <x:v>・最大使用回数: 1</x:v>
       </x:c>
       <x:c r="E5" s="6" t="str">
-        <x:v>・最大使用回数: 1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="30" customHeight="1">
-      <x:c r="A6" s="8" t="str"/>
+        <x:v>最大使用回数：1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="8"/>
       <x:c r="B6" s="6" t="str">
         <x:v>・재사용 대기시간 : 6초</x:v>
       </x:c>
@@ -1544,52 +1617,70 @@
         <x:v>・再使用待機時間: 6秒</x:v>
       </x:c>
       <x:c r="E6" s="6" t="str">
-        <x:v>・再使用待機時間: 6秒</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="30" customHeight="1">
-      <x:c r="A7" s="8" t="str"/>
-      <x:c r="B7" s="6" t="str">
+        <x:v>再使用待機時間：6秒</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="8"/>
+      <x:c r="B7" s="6"/>
+      <x:c r="C7" s="6"/>
+      <x:c r="D7" s="6"/>
+      <x:c r="E7" s="6" t="str">
+        <x:v>・打撃ダメージ1042.78%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="8"/>
+      <x:c r="B8" s="6"/>
+      <x:c r="C8" s="6"/>
+      <x:c r="D8" s="6"/>
+      <x:c r="E8" s="6" t="str">
+        <x:v>・PVP打撃ダメージ521.39%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="8"/>
+      <x:c r="B9" s="6" t="str">
         <x:v>・최대 11 타격</x:v>
       </x:c>
-      <x:c r="C7" s="6" t="str">
+      <x:c r="C9" s="6" t="str">
         <x:v>・Max 11 hits</x:v>
       </x:c>
-      <x:c r="D7" s="6" t="str">
+      <x:c r="D9" s="6" t="str">
         <x:v>・最大11ヒット</x:v>
       </x:c>
-      <x:c r="E7" s="6" t="str">
-        <x:v>・最大11ヒット</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="30" customHeight="1">
-      <x:c r="A8" s="8" t="str"/>
-      <x:c r="B8" s="6" t="str">
+      <x:c r="E9" s="6" t="str">
+        <x:v>・最大11打撃</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" s="5"/>
+      <x:c r="B10" s="5" t="str">
         <x:v>・기술 사용 중 슈퍼 아머</x:v>
       </x:c>
-      <x:c r="C8" s="6" t="str">
+      <x:c r="C10" s="5" t="str">
         <x:v>・Super Armor during skill use</x:v>
       </x:c>
-      <x:c r="D8" s="6" t="str">
+      <x:c r="D10" s="5" t="str">
         <x:v>・技術使用時のスーパーアーマー</x:v>
       </x:c>
-      <x:c r="E8" s="6" t="str">
-        <x:v>・技術使用時のスーパーアーマー</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="30" customHeight="1">
-      <x:c r="A9" s="8" t="str"/>
-      <x:c r="B9" s="6" t="str">
+      <x:c r="E10" s="5" t="str">
+        <x:v>・スキル使用中、スーパーアーマー</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11" s="5"/>
+      <x:c r="B11" s="5" t="str">
         <x:v>・마지막 타격 성공 시 띄우기</x:v>
       </x:c>
-      <x:c r="C9" s="6" t="str">
+      <x:c r="C11" s="5" t="str">
         <x:v>・On last successful hit Knock-up</x:v>
       </x:c>
-      <x:c r="D9" s="6" t="str">
+      <x:c r="D11" s="5" t="str">
         <x:v>・最後に成功したヒット時浮かせ</x:v>
       </x:c>
-      <x:c r="E9" s="6" t="str">
-        <x:v>・最後に成功したヒット時浮かせ</x:v>
+      <x:c r="E11" s="5" t="str">
+        <x:v>・最後の打撃成功時、浮かす</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1609,7 +1700,7 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="4" t="str"/>
+      <x:c r="A1" s="4"/>
       <x:c r="B1" s="4" t="str">
         <x:v>韓国語</x:v>
       </x:c>
@@ -1637,7 +1728,7 @@
         <x:v>連枷旋風</x:v>
       </x:c>
       <x:c r="E2" s="6" t="str">
-        <x:v>連枷旋風</x:v>
+        <x:v>唐棹軟風</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="30" customHeight="1">
@@ -1654,11 +1745,11 @@
         <x:v>PvE ｜系列 無欠 鮮明 洗練された</x:v>
       </x:c>
       <x:c r="E3" s="6" t="str">
-        <x:v>PvE ｜系列 無欠 鮮明 洗練された</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="30" customHeight="1">
-      <x:c r="A4" s="8" t="str"/>
+        <x:v>PvE</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A4" s="8"/>
       <x:c r="B4" s="6" t="str">
         <x:v>"몸을 회전하며 초화선으로 적을 여러 번 벤다."</x:v>
       </x:c>
@@ -1669,11 +1760,11 @@
         <x:v>「体を回転させながら狐扇で敵を複数回斬りつける。」</x:v>
       </x:c>
       <x:c r="E4" s="6" t="str">
-        <x:v>「体を回転させながら狐扇で敵を複数回斬りつける。」</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="30" customHeight="1">
-      <x:c r="A5" s="8" t="str"/>
+        <x:v>体を回転させ、招画扇で敵を何度も斬りつける。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="8"/>
       <x:c r="B5" s="6" t="str">
         <x:v>・최대 사용 횟수 : 1</x:v>
       </x:c>
@@ -1684,11 +1775,11 @@
         <x:v>・最大使用回数: 1</x:v>
       </x:c>
       <x:c r="E5" s="6" t="str">
-        <x:v>・最大使用回数: 1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="30" customHeight="1">
-      <x:c r="A6" s="8" t="str"/>
+        <x:v>最大使用回数：1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="8"/>
       <x:c r="B6" s="6" t="str">
         <x:v>・재사용 대기시간 : 6초</x:v>
       </x:c>
@@ -1699,52 +1790,70 @@
         <x:v>・再使用待機時間: 6秒</x:v>
       </x:c>
       <x:c r="E6" s="6" t="str">
-        <x:v>・再使用待機時間: 6秒</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="30" customHeight="1">
-      <x:c r="A7" s="8" t="str"/>
-      <x:c r="B7" s="6" t="str">
+        <x:v>再使用待機時間：6秒</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="8"/>
+      <x:c r="B7" s="6"/>
+      <x:c r="C7" s="6"/>
+      <x:c r="D7" s="6"/>
+      <x:c r="E7" s="6" t="str">
+        <x:v>・打撃ダメージ915.64%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="8"/>
+      <x:c r="B8" s="6"/>
+      <x:c r="C8" s="6"/>
+      <x:c r="D8" s="6"/>
+      <x:c r="E8" s="6" t="str">
+        <x:v>・PVP打撃ダメージ457.82%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="8"/>
+      <x:c r="B9" s="6" t="str">
         <x:v>・최대 6 타격</x:v>
       </x:c>
-      <x:c r="C7" s="6" t="str">
+      <x:c r="C9" s="6" t="str">
         <x:v>・Max 6 hits</x:v>
       </x:c>
-      <x:c r="D7" s="6" t="str">
+      <x:c r="D9" s="6" t="str">
         <x:v>・最大6ヒット</x:v>
       </x:c>
-      <x:c r="E7" s="6" t="str">
-        <x:v>・最大6ヒット</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="30" customHeight="1">
-      <x:c r="A8" s="8" t="str"/>
-      <x:c r="B8" s="6" t="str">
+      <x:c r="E9" s="6" t="str">
+        <x:v>・最大6打撃</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" s="5"/>
+      <x:c r="B10" s="5" t="str">
         <x:v>・기술 사용 중 슈퍼 아머 , 잡기 불가</x:v>
       </x:c>
-      <x:c r="C8" s="6" t="str">
+      <x:c r="C10" s="5" t="str">
         <x:v>・Super Armor , Grab Immunity during skill use</x:v>
       </x:c>
-      <x:c r="D8" s="6" t="str">
+      <x:c r="D10" s="5" t="str">
         <x:v>・スーパーアーマー、技術使用時の獲得免疫</x:v>
       </x:c>
-      <x:c r="E8" s="6" t="str">
-        <x:v>・スーパーアーマー、技術使用時の獲得免疫</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="30" customHeight="1">
-      <x:c r="A9" s="8" t="str"/>
-      <x:c r="B9" s="6" t="str">
+      <x:c r="E10" s="5" t="str">
+        <x:v>・スキル使用中、スーパーアーマー、キャッチ不可</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11" s="5"/>
+      <x:c r="B11" s="5" t="str">
         <x:v>・타격 성공 시 경직</x:v>
       </x:c>
-      <x:c r="C9" s="6" t="str">
+      <x:c r="C11" s="5" t="str">
         <x:v>・On successful hit Stiffness</x:v>
       </x:c>
-      <x:c r="D9" s="6" t="str">
+      <x:c r="D11" s="5" t="str">
         <x:v>・ヒット成功時の剛性</x:v>
       </x:c>
-      <x:c r="E9" s="6" t="str">
-        <x:v>・ヒット成功時の剛性</x:v>
+      <x:c r="E11" s="5" t="str">
+        <x:v>・打撃成功時、硬直</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1764,7 +1873,7 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="4" t="str"/>
+      <x:c r="A1" s="4"/>
       <x:c r="B1" s="4" t="str">
         <x:v>韓国語</x:v>
       </x:c>
@@ -1809,11 +1918,11 @@
         <x:v>「鍛え上げたスペルパワーを集めて自身を強化する」</x:v>
       </x:c>
       <x:c r="E3" s="6" t="str">
-        <x:v>「鍛え上げたスペルパワーを集めて自身を強化する」</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="30" customHeight="1">
-      <x:c r="A4" s="8" t="str"/>
+        <x:v>修練した呪力を集めて自身を強化する。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="15" hidden="0" customHeight="1">
+      <x:c r="A4" s="8"/>
       <x:c r="B4" s="6" t="str">
         <x:v>・최대 사용 횟수 : 1</x:v>
       </x:c>
@@ -1824,11 +1933,11 @@
         <x:v>・最大使用回数: 1</x:v>
       </x:c>
       <x:c r="E4" s="6" t="str">
-        <x:v>・最大使用回数: 1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="30" customHeight="1">
-      <x:c r="A5" s="8" t="str"/>
+        <x:v>最大使用回数：1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="8"/>
       <x:c r="B5" s="6" t="str">
         <x:v>・재사용 대기 시간 : 90초</x:v>
       </x:c>
@@ -1839,11 +1948,11 @@
         <x:v>・再使用待機時間: 90秒</x:v>
       </x:c>
       <x:c r="E5" s="6" t="str">
-        <x:v>・再使用待機時間: 90秒</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="30" customHeight="1">
-      <x:c r="A6" s="8" t="str"/>
+        <x:v>再使用待機時間：93秒</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="8"/>
       <x:c r="B6" s="6" t="str">
         <x:v>・10초 간 2초 마다 생명력 회복 115~400</x:v>
       </x:c>
@@ -1854,11 +1963,11 @@
         <x:v>・10秒間、2秒ごとに生命力回復115~400</x:v>
       </x:c>
       <x:c r="E6" s="6" t="str">
-        <x:v>・10秒間、2秒ごとに生命力回復115~400</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="30" customHeight="1">
-      <x:c r="A7" s="8" t="str"/>
+        <x:v>・10秒間、2秒ごとにHP250回復</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="8"/>
       <x:c r="B7" s="6" t="str">
         <x:v>・30초 간 공격력 +43~100</x:v>
       </x:c>
@@ -1869,11 +1978,11 @@
         <x:v>・30秒間AP +43~100</x:v>
       </x:c>
       <x:c r="E7" s="6" t="str">
-        <x:v>・30秒間AP +43~100</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="30" customHeight="1">
-      <x:c r="A8" s="8" t="str"/>
+        <x:v>・30秒間、攻撃力+70</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="8"/>
       <x:c r="B8" s="6" t="str">
         <x:v>・30초 간 방어력 +43~100</x:v>
       </x:c>
@@ -1884,11 +1993,11 @@
         <x:v>・30秒間DP+43~100</x:v>
       </x:c>
       <x:c r="E8" s="6" t="str">
-        <x:v>・30秒間DP+43~100</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="30" customHeight="1">
-      <x:c r="A9" s="8" t="str"/>
+        <x:v>・30秒間、防御力+70</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="8"/>
       <x:c r="B9" s="6" t="str">
         <x:v>・30초 간 치명타 피해량 +50%</x:v>
       </x:c>
@@ -1899,11 +2008,11 @@
         <x:v>・30秒間致命打被害量+50%</x:v>
       </x:c>
       <x:c r="E9" s="6" t="str">
-        <x:v>・30秒間致命打被害量+50%</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="30" customHeight="1">
-      <x:c r="A10" s="8" t="str"/>
+        <x:v>・30秒間、クリティカルダメージ量+50%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" s="8"/>
       <x:c r="B10" s="6" t="str">
         <x:v>・30초 간 흑정령 기술 피해량 +20%</x:v>
       </x:c>
@@ -1914,11 +2023,11 @@
         <x:v>・30秒間、闇の精霊技術被害量+20%</x:v>
       </x:c>
       <x:c r="E10" s="6" t="str">
-        <x:v>・30秒間、闇の精霊技術被害量+20%</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="30" customHeight="1">
-      <x:c r="A11" s="8" t="str"/>
+        <x:v>・30秒間、闇の精霊スキルダメージ量+20%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11" s="8"/>
       <x:c r="B11" s="6" t="str">
         <x:v>・기술 사용 시 30초 간 회피 기술 재사용 시간 2초 감소</x:v>
       </x:c>
@@ -1929,7 +2038,7 @@
         <x:v>・回避技術の再使用待機時間短縮 2秒、30秒間</x:v>
       </x:c>
       <x:c r="E11" s="6" t="str">
-        <x:v>・回避技術の再使用待機時間短縮 2秒、30秒間</x:v>
+        <x:v>・スキル使用時30秒間、回避スキル再使用時間2秒減少</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1949,7 +2058,7 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="4" t="str"/>
+      <x:c r="A1" s="4"/>
       <x:c r="B1" s="4" t="str">
         <x:v>韓国語</x:v>
       </x:c>
@@ -1994,11 +2103,11 @@
         <x:v>PvE PvP ｜系列 無欠 鮮明 洗練された</x:v>
       </x:c>
       <x:c r="E3" s="6" t="str">
-        <x:v>PvE PvP ｜系列 無欠 鮮明 洗練された</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="30" customHeight="1">
-      <x:c r="A4" s="8" t="str"/>
+        <x:v>PvE PvP</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A4" s="8"/>
       <x:c r="B4" s="6" t="str">
         <x:v>"앞으로 뛰어 부적의 낙인을 찍은 뒤 멀어지며 도력을 폭발시킨다."</x:v>
       </x:c>
@@ -2009,11 +2118,11 @@
         <x:v>「前にジャンプして護符のブランドをマークし、その後離れて護符パワーを爆発させます。」</x:v>
       </x:c>
       <x:c r="E4" s="6" t="str">
-        <x:v>「前にジャンプして護符のブランドをマークし、その後離れて護符パワーを爆発させます。」</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="30" customHeight="1">
-      <x:c r="A5" s="8" t="str"/>
+        <x:v>前方に向かって走って霊符の烙印を刻んだ後、離れながら道力を爆発させる。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="8"/>
       <x:c r="B5" s="6" t="str">
         <x:v>・최대 사용 횟수 : 1</x:v>
       </x:c>
@@ -2024,11 +2133,11 @@
         <x:v>・最大使用回数: 1</x:v>
       </x:c>
       <x:c r="E5" s="6" t="str">
-        <x:v>・最大使用回数: 1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="30" customHeight="1">
-      <x:c r="A6" s="8" t="str"/>
+        <x:v>最大使用回数：1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="8"/>
       <x:c r="B6" s="6" t="str">
         <x:v>・재사용 대기시간 : 15초</x:v>
       </x:c>
@@ -2039,52 +2148,70 @@
         <x:v>・再使用待機時間: 15秒</x:v>
       </x:c>
       <x:c r="E6" s="6" t="str">
-        <x:v>・再使用待機時間: 15秒</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="30" customHeight="1">
-      <x:c r="A7" s="8" t="str"/>
-      <x:c r="B7" s="6" t="str">
+        <x:v>再使用待機時間：15秒</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="8"/>
+      <x:c r="B7" s="6"/>
+      <x:c r="C7" s="6"/>
+      <x:c r="D7" s="6"/>
+      <x:c r="E7" s="6" t="str">
+        <x:v>・打撃ダメージ2700%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="8"/>
+      <x:c r="B8" s="6"/>
+      <x:c r="C8" s="6"/>
+      <x:c r="D8" s="6"/>
+      <x:c r="E8" s="6" t="str">
+        <x:v>・PVP打撃ダメージ1350%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="8"/>
+      <x:c r="B9" s="6" t="str">
         <x:v>・최대 4 타격</x:v>
       </x:c>
-      <x:c r="C7" s="6" t="str">
+      <x:c r="C9" s="6" t="str">
         <x:v>・Max 4 hits</x:v>
       </x:c>
-      <x:c r="D7" s="6" t="str">
+      <x:c r="D9" s="6" t="str">
         <x:v>・最大4ヒット</x:v>
       </x:c>
-      <x:c r="E7" s="6" t="str">
-        <x:v>・最大4ヒット</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="30" customHeight="1">
-      <x:c r="A8" s="8" t="str"/>
-      <x:c r="B8" s="6" t="str">
+      <x:c r="E9" s="6" t="str">
+        <x:v>・最大4打撃</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10"/>
+      <x:c r="B10" t="str">
         <x:v>・기술 사용 중 슈퍼 아머</x:v>
       </x:c>
-      <x:c r="C8" s="6" t="str">
+      <x:c r="C10" t="str">
         <x:v>・Super Armor during skill use</x:v>
       </x:c>
-      <x:c r="D8" s="6" t="str">
+      <x:c r="D10" t="str">
         <x:v>・技術使用時のスーパーアーマー</x:v>
       </x:c>
-      <x:c r="E8" s="6" t="str">
-        <x:v>・技術使用時のスーパーアーマー</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="30" customHeight="1">
-      <x:c r="A9" s="8" t="str"/>
-      <x:c r="B9" s="6" t="str">
+      <x:c r="E10" t="str">
+        <x:v>・スキル使用中、スーパーアーマー</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11"/>
+      <x:c r="B11" t="str">
         <x:v>・타격 성공 시 경직</x:v>
       </x:c>
-      <x:c r="C9" s="6" t="str">
+      <x:c r="C11" t="str">
         <x:v>・On successful hit Stiffness</x:v>
       </x:c>
-      <x:c r="D9" s="6" t="str">
+      <x:c r="D11" t="str">
         <x:v>・ヒット成功時の剛性</x:v>
       </x:c>
-      <x:c r="E9" s="6" t="str">
-        <x:v>・ヒット成功時の剛性</x:v>
+      <x:c r="E11" t="str">
+        <x:v>・打撃成功時、硬直</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2104,7 +2231,7 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="4" t="str"/>
+      <x:c r="A1" s="4"/>
       <x:c r="B1" s="4" t="str">
         <x:v>韓国語</x:v>
       </x:c>
@@ -2132,7 +2259,7 @@
         <x:v>南風の舞</x:v>
       </x:c>
       <x:c r="E2" s="6" t="str">
-        <x:v>南風の舞</x:v>
+        <x:v>裏風の舞</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="30" customHeight="1">
@@ -2149,11 +2276,11 @@
         <x:v>PvE PvP ｜系列 無欠 鮮明 洗練された</x:v>
       </x:c>
       <x:c r="E3" s="6" t="str">
-        <x:v>PvE PvP ｜系列 無欠 鮮明 洗練された</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="30" customHeight="1">
-      <x:c r="A4" s="8" t="str"/>
+        <x:v>PvE PvP</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="15" hidden="0" customHeight="1">
+      <x:c r="A4" s="8"/>
       <x:c r="B4" s="6" t="str">
         <x:v>"초화선에 깃든 여우불을 전방으로 방출하여 적을 베어낸다."</x:v>
       </x:c>
@@ -2164,11 +2291,11 @@
         <x:v>「狐扇に込められたフォックスファイアを前方に放ち、敵を斬り裂く。」</x:v>
       </x:c>
       <x:c r="E4" s="6" t="str">
-        <x:v>「狐扇に込められたフォックスファイアを前方に放ち、敵を斬り裂く。」</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="30" customHeight="1">
-      <x:c r="A5" s="8" t="str"/>
+        <x:v>招画扇に宿った狐火を前方に放出して敵を斬りつける。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="8"/>
       <x:c r="B5" s="6" t="str">
         <x:v>・최대 사용 횟수 : 1</x:v>
       </x:c>
@@ -2179,11 +2306,11 @@
         <x:v>・最大使用回数: 1</x:v>
       </x:c>
       <x:c r="E5" s="6" t="str">
-        <x:v>・最大使用回数: 1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="30" customHeight="1">
-      <x:c r="A6" s="8" t="str"/>
+        <x:v>最大使用回数：1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="8"/>
       <x:c r="B6" s="6" t="str">
         <x:v>・재사용 대기시간 : 15초</x:v>
       </x:c>
@@ -2194,52 +2321,70 @@
         <x:v>・再使用待機時間: 15秒</x:v>
       </x:c>
       <x:c r="E6" s="6" t="str">
-        <x:v>・再使用待機時間: 15秒</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="30" customHeight="1">
-      <x:c r="A7" s="8" t="str"/>
-      <x:c r="B7" s="6" t="str">
+        <x:v>再使用待機時間：15秒</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="8"/>
+      <x:c r="B7" s="6"/>
+      <x:c r="C7" s="6"/>
+      <x:c r="D7" s="6"/>
+      <x:c r="E7" s="6" t="str">
+        <x:v>・打撃ダメージ2504%x2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="8"/>
+      <x:c r="B8" s="6"/>
+      <x:c r="C8" s="6"/>
+      <x:c r="D8" s="6"/>
+      <x:c r="E8" s="6" t="str">
+        <x:v>・PVP打撃ダメージ1252%x2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="8"/>
+      <x:c r="B9" s="6" t="str">
         <x:v>・최대 2 타격</x:v>
       </x:c>
-      <x:c r="C7" s="6" t="str">
+      <x:c r="C9" s="6" t="str">
         <x:v>・Max 2 hits</x:v>
       </x:c>
-      <x:c r="D7" s="6" t="str">
+      <x:c r="D9" s="6" t="str">
         <x:v>・最大2ヒット</x:v>
       </x:c>
-      <x:c r="E7" s="6" t="str">
-        <x:v>・最大2ヒット</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="30" customHeight="1">
-      <x:c r="A8" s="8" t="str"/>
-      <x:c r="B8" s="6" t="str">
+      <x:c r="E9" s="6" t="str">
+        <x:v>・最大2打撃</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10"/>
+      <x:c r="B10" t="str">
         <x:v>・기술 사용 중 전방 가드</x:v>
       </x:c>
-      <x:c r="C8" s="6" t="str">
+      <x:c r="C10" t="str">
         <x:v>・During skill use Forward Guard</x:v>
       </x:c>
-      <x:c r="D8" s="6" t="str">
+      <x:c r="D10" t="str">
         <x:v>・技術使用時 前方ガード</x:v>
       </x:c>
-      <x:c r="E8" s="6" t="str">
-        <x:v>・技術使用時 前方ガード</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="30" customHeight="1">
-      <x:c r="A9" s="8" t="str"/>
-      <x:c r="B9" s="6" t="str">
+      <x:c r="E10" t="str">
+        <x:v>・スキル使用中、前方ガード</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11"/>
+      <x:c r="B11" t="str">
         <x:v>・타격 성공 시 경직</x:v>
       </x:c>
-      <x:c r="C9" s="6" t="str">
+      <x:c r="C11" t="str">
         <x:v>・On successful hit Stiffness</x:v>
       </x:c>
-      <x:c r="D9" s="6" t="str">
+      <x:c r="D11" t="str">
         <x:v>・ヒット成功時の剛性</x:v>
       </x:c>
-      <x:c r="E9" s="6" t="str">
-        <x:v>・ヒット成功時の剛性</x:v>
+      <x:c r="E11" t="str">
+        <x:v>・打撃成功時、硬直</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2259,7 +2404,7 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="4" t="str"/>
+      <x:c r="A1" s="4"/>
       <x:c r="B1" s="4" t="str">
         <x:v>韓国語</x:v>
       </x:c>
@@ -2287,7 +2432,7 @@
         <x:v>霊符：宝具</x:v>
       </x:c>
       <x:c r="E2" s="6" t="str">
-        <x:v>霊符：宝具</x:v>
+        <x:v>霊符：報仇</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="30" customHeight="1">
@@ -2304,11 +2449,11 @@
         <x:v>PvE PvP ｜系列 守護 無欠 鮮明</x:v>
       </x:c>
       <x:c r="E3" s="6" t="str">
-        <x:v>PvE PvP ｜系列 守護 無欠 鮮明</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="30" customHeight="1">
-      <x:c r="A4" s="8" t="str"/>
+        <x:v>PvE PvP</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="15" hidden="0" customHeight="1">
+      <x:c r="A4" s="8"/>
       <x:c r="B4" s="6" t="str">
         <x:v>"도력을 증폭시켜 전방의 적들을 휩쓸어버린다."</x:v>
       </x:c>
@@ -2319,11 +2464,11 @@
         <x:v>「護符パワーを増幅させて前方の敵を一掃する。」</x:v>
       </x:c>
       <x:c r="E4" s="6" t="str">
-        <x:v>「護符パワーを増幅させて前方の敵を一掃する。」</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="30" customHeight="1">
-      <x:c r="A5" s="8" t="str"/>
+        <x:v>道力を増幅させて前方の敵を一掃する。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="8"/>
       <x:c r="B5" s="6" t="str">
         <x:v>・최대 사용 횟수 : 1</x:v>
       </x:c>
@@ -2334,11 +2479,11 @@
         <x:v>・最大使用回数: 1</x:v>
       </x:c>
       <x:c r="E5" s="6" t="str">
-        <x:v>・最大使用回数: 1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="30" customHeight="1">
-      <x:c r="A6" s="8" t="str"/>
+        <x:v>最大使用回数：1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="8"/>
       <x:c r="B6" s="6" t="str">
         <x:v>・재사용 대기시간 : 16초</x:v>
       </x:c>
@@ -2349,82 +2494,100 @@
         <x:v>・再使用待機時間: 16秒</x:v>
       </x:c>
       <x:c r="E6" s="6" t="str">
-        <x:v>・再使用待機時間: 16秒</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="30" customHeight="1">
-      <x:c r="A7" s="8" t="str"/>
-      <x:c r="B7" s="6" t="str">
+        <x:v>再使用待機時間：16秒</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="8"/>
+      <x:c r="B7" s="6"/>
+      <x:c r="C7" s="6"/>
+      <x:c r="D7" s="6"/>
+      <x:c r="E7" s="6" t="str">
+        <x:v>・打撃ダメージ2251%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="8"/>
+      <x:c r="B8" s="6"/>
+      <x:c r="C8" s="6"/>
+      <x:c r="D8" s="6"/>
+      <x:c r="E8" s="6" t="str">
+        <x:v>・PVP打撃ダメージ1125.5%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="8"/>
+      <x:c r="B9" s="6" t="str">
         <x:v>・최대 5 타격</x:v>
       </x:c>
-      <x:c r="C7" s="6" t="str">
+      <x:c r="C9" s="6" t="str">
         <x:v>・Max 5 hits</x:v>
       </x:c>
-      <x:c r="D7" s="6" t="str">
+      <x:c r="D9" s="6" t="str">
         <x:v>・最大5ヒット</x:v>
       </x:c>
-      <x:c r="E7" s="6" t="str">
-        <x:v>・最大5ヒット</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="30" customHeight="1">
-      <x:c r="A8" s="8" t="str"/>
-      <x:c r="B8" s="6" t="str">
+      <x:c r="E9" s="6" t="str">
+        <x:v>・最大5打撃</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" s="8"/>
+      <x:c r="B10" s="6" t="str">
         <x:v>・즉시 발동 기술</x:v>
       </x:c>
-      <x:c r="C8" s="6" t="str">
+      <x:c r="C10" s="6" t="str">
         <x:v>・Instant Activation Skill</x:v>
       </x:c>
-      <x:c r="D8" s="6" t="str">
+      <x:c r="D10" s="6" t="str">
         <x:v>・即時発動技術</x:v>
       </x:c>
-      <x:c r="E8" s="6" t="str">
-        <x:v>・即時発動技術</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="30" customHeight="1">
-      <x:c r="A9" s="8" t="str"/>
-      <x:c r="B9" s="6" t="str">
+      <x:c r="E10" s="6" t="str">
+        <x:v>・即時発動スキル</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11" s="8"/>
+      <x:c r="B11" s="6" t="str">
         <x:v>・기술 사용 중 전방 가드</x:v>
       </x:c>
-      <x:c r="C9" s="6" t="str">
+      <x:c r="C11" s="6" t="str">
         <x:v>・During skill use Forward Guard</x:v>
       </x:c>
-      <x:c r="D9" s="6" t="str">
+      <x:c r="D11" s="6" t="str">
         <x:v>・技術使用時 前方ガード</x:v>
       </x:c>
-      <x:c r="E9" s="6" t="str">
-        <x:v>・技術使用時 前方ガード</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="30" customHeight="1">
-      <x:c r="A10" s="8" t="str"/>
-      <x:c r="B10" s="6" t="str">
+      <x:c r="E11" s="6" t="str">
+        <x:v>・スキル使用中、前方ガード</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
+      <x:c r="A12"/>
+      <x:c r="B12" t="str">
         <x:v>・타격 성공 시 넉다운</x:v>
       </x:c>
-      <x:c r="C10" s="6" t="str">
+      <x:c r="C12" t="str">
         <x:v>・On successful hit Knockdown</x:v>
       </x:c>
-      <x:c r="D10" s="6" t="str">
+      <x:c r="D12" t="str">
         <x:v>・ヒットノックダウン成功時</x:v>
       </x:c>
-      <x:c r="E10" s="6" t="str">
-        <x:v>・ヒットノックダウン成功時</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="30" customHeight="1">
-      <x:c r="A11" s="8" t="str"/>
-      <x:c r="B11" s="6" t="str">
+      <x:c r="E12" t="str">
+        <x:v>・打撃成功時、ノックダウン</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="15" hidden="0" customHeight="1">
+      <x:c r="A13"/>
+      <x:c r="B13" t="str">
         <x:v>・기술 사용 중 모험가에게 받는 최종 피해량 40% 감소</x:v>
       </x:c>
-      <x:c r="C11" s="6" t="str">
+      <x:c r="C13" t="str">
         <x:v>・Final damage received from Adventurers during skill use 40% decrease</x:v>
       </x:c>
-      <x:c r="D11" s="6" t="str">
+      <x:c r="D13" t="str">
         <x:v>・技術使用時に冒険者から受ける最終ダメージ40%減少</x:v>
       </x:c>
-      <x:c r="E11" s="6" t="str">
-        <x:v>・技術使用時に冒険者から受ける最終ダメージ40%減少</x:v>
+      <x:c r="E13" t="str">
+        <x:v>・スキル使用中、冒険者から受ける最終ダメージ量40%減少</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2802,7 +2965,7 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="4" t="str"/>
+      <x:c r="A1" s="4"/>
       <x:c r="B1" s="4" t="str">
         <x:v>韓国語</x:v>
       </x:c>
@@ -2830,7 +2993,7 @@
         <x:v>爆裂の舞</x:v>
       </x:c>
       <x:c r="E2" s="6" t="str">
-        <x:v>爆裂の舞</x:v>
+        <x:v>爆翻の舞</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="30" customHeight="1">
@@ -2847,11 +3010,11 @@
         <x:v>PvE PvP ｜系列 守護 無欠 鮮明</x:v>
       </x:c>
       <x:c r="E3" s="6" t="str">
-        <x:v>PvE PvP ｜系列 守護 無欠 鮮明</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="30" customHeight="1">
-      <x:c r="A4" s="8" t="str"/>
+        <x:v>PvE PvP</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A4" s="8"/>
       <x:c r="B4" s="6" t="str">
         <x:v>"여우눈에 비친 여우신령을 초화선의 여우불에 강신하게 한다. 이후 여우신령의 발톱을 흉내 내 전방의 적을 쓸어버린다."</x:v>
       </x:c>
@@ -2862,11 +3025,11 @@
         <x:v>「キツネの目に映るキツネの精を呼び出し、キツネ団扇のキツネの火に降下する。そして、キツネの精の爪を真似て前方の敵を一掃する。」</x:v>
       </x:c>
       <x:c r="E4" s="6" t="str">
-        <x:v>「キツネの目に映るキツネの精を呼び出し、キツネ団扇のキツネの火に降下する。そして、キツネの精の爪を真似て前方の敵を一掃する。」</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="30" customHeight="1">
-      <x:c r="A5" s="8" t="str"/>
+        <x:v>狐の目に映った狐神霊を招画扇の狐火に降神させた後、狐神霊の爪を模して前方の敵を一掃する。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="8"/>
       <x:c r="B5" s="6" t="str">
         <x:v>・최대 사용 횟수 : 1</x:v>
       </x:c>
@@ -2877,11 +3040,11 @@
         <x:v>・最大使用回数: 1</x:v>
       </x:c>
       <x:c r="E5" s="6" t="str">
-        <x:v>・最大使用回数: 1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="30" customHeight="1">
-      <x:c r="A6" s="8" t="str"/>
+        <x:v>最大使用回数：1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="8"/>
       <x:c r="B6" s="6" t="str">
         <x:v>・재사용 대기시간 : 15초</x:v>
       </x:c>
@@ -2892,52 +3055,70 @@
         <x:v>・再使用待機時間: 15秒</x:v>
       </x:c>
       <x:c r="E6" s="6" t="str">
-        <x:v>・再使用待機時間: 15秒</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="30" customHeight="1">
-      <x:c r="A7" s="8" t="str"/>
-      <x:c r="B7" s="6" t="str">
+        <x:v>再使用待機時間：15秒</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="8"/>
+      <x:c r="B7" s="6"/>
+      <x:c r="C7" s="6"/>
+      <x:c r="D7" s="6"/>
+      <x:c r="E7" s="6" t="str">
+        <x:v>・打撃ダメージ2547%x2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="8"/>
+      <x:c r="B8" s="6"/>
+      <x:c r="C8" s="6"/>
+      <x:c r="D8" s="6"/>
+      <x:c r="E8" s="6" t="str">
+        <x:v>・PVP打撃ダメージ1273.5%x2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="8"/>
+      <x:c r="B9" s="6" t="str">
         <x:v>・최대 2 타격</x:v>
       </x:c>
-      <x:c r="C7" s="6" t="str">
+      <x:c r="C9" s="6" t="str">
         <x:v>・Max 2 hits</x:v>
       </x:c>
-      <x:c r="D7" s="6" t="str">
+      <x:c r="D9" s="6" t="str">
         <x:v>・最大2ヒット</x:v>
       </x:c>
-      <x:c r="E7" s="6" t="str">
-        <x:v>・最大2ヒット</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="30" customHeight="1">
-      <x:c r="A8" s="8" t="str"/>
-      <x:c r="B8" s="6" t="str">
+      <x:c r="E9" s="6" t="str">
+        <x:v>・最大2打撃</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10"/>
+      <x:c r="B10" t="str">
         <x:v>・기술 사용 중 슈퍼 아머</x:v>
       </x:c>
-      <x:c r="C8" s="6" t="str">
+      <x:c r="C10" t="str">
         <x:v>・Super Armor during skill use</x:v>
       </x:c>
-      <x:c r="D8" s="6" t="str">
+      <x:c r="D10" t="str">
         <x:v>・技術使用時のスーパーアーマー</x:v>
       </x:c>
-      <x:c r="E8" s="6" t="str">
-        <x:v>・技術使用時のスーパーアーマー</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="30" customHeight="1">
-      <x:c r="A9" s="8" t="str"/>
-      <x:c r="B9" s="6" t="str">
+      <x:c r="E10" t="str">
+        <x:v>・スキル使用中、スーパーアーマー</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11"/>
+      <x:c r="B11" t="str">
         <x:v>・타격 성공 시 넉다운</x:v>
       </x:c>
-      <x:c r="C9" s="6" t="str">
+      <x:c r="C11" t="str">
         <x:v>・On successful hit Knockdown</x:v>
       </x:c>
-      <x:c r="D9" s="6" t="str">
+      <x:c r="D11" t="str">
         <x:v>・ヒットノックダウン成功時</x:v>
       </x:c>
-      <x:c r="E9" s="6" t="str">
-        <x:v>・ヒットノックダウン成功時</x:v>
+      <x:c r="E11" t="str">
+        <x:v>・打撃成功時、ノックダウン</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3332,7 +3513,7 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="4" t="str"/>
+      <x:c r="A1" s="4"/>
       <x:c r="B1" s="4" t="str">
         <x:v>韓国語</x:v>
       </x:c>
@@ -3377,11 +3558,11 @@
         <x:v>PvE PvP ｜系列 無欠 鮮明 かすかな</x:v>
       </x:c>
       <x:c r="E3" s="6" t="str">
-        <x:v>PvE PvP ｜系列 無欠 鮮明 かすかな</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="30" customHeight="1">
-      <x:c r="A4" s="8" t="str"/>
+        <x:v>PvE PvP</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A4" s="8"/>
       <x:c r="B4" s="6" t="str">
         <x:v>"축지로 상대에게 접근해 일정 시간 후 폭발하는 령부를 붙인다."</x:v>
       </x:c>
@@ -3392,11 +3573,11 @@
         <x:v>「フットワークで相手に近づき、一定時間後に爆発する護符を付ける。」</x:v>
       </x:c>
       <x:c r="E4" s="6" t="str">
-        <x:v>「フットワークで相手に近づき、一定時間後に爆発する護符を付ける。」</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="30" customHeight="1">
-      <x:c r="A5" s="8" t="str"/>
+        <x:v>縮地で相手に接近し一定時間が経過したら爆発する霊符を貼る。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="8"/>
       <x:c r="B5" s="6" t="str">
         <x:v>・최대 사용 횟수 : 1</x:v>
       </x:c>
@@ -3407,11 +3588,11 @@
         <x:v>・最大使用回数: 1</x:v>
       </x:c>
       <x:c r="E5" s="6" t="str">
-        <x:v>・最大使用回数: 1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="30" customHeight="1">
-      <x:c r="A6" s="8" t="str"/>
+        <x:v>最大使用回数：1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="8"/>
       <x:c r="B6" s="6" t="str">
         <x:v>・재사용 대기시간 : 6초</x:v>
       </x:c>
@@ -3422,97 +3603,133 @@
         <x:v>・再使用待機時間: 6秒</x:v>
       </x:c>
       <x:c r="E6" s="6" t="str">
-        <x:v>・再使用待機時間: 6秒</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="30" customHeight="1">
-      <x:c r="A7" s="8" t="str"/>
-      <x:c r="B7" s="6" t="str">
+        <x:v>再使用待機時間：6秒</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="8"/>
+      <x:c r="B7" s="6"/>
+      <x:c r="C7" s="6"/>
+      <x:c r="D7" s="6"/>
+      <x:c r="E7" s="6" t="str">
+        <x:v>・打撃ダメージ2237.09%x2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="8"/>
+      <x:c r="B8" s="6"/>
+      <x:c r="C8" s="6"/>
+      <x:c r="D8" s="6"/>
+      <x:c r="E8" s="6" t="str">
+        <x:v>・PVP打撃ダメージ1118.55%x2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="8"/>
+      <x:c r="B9" s="6" t="str">
         <x:v>・기술 재사용 시 즉시 발동 가능</x:v>
       </x:c>
-      <x:c r="C7" s="6" t="str">
+      <x:c r="C9" s="6" t="str">
         <x:v>・Instant Activation available when re-using skill</x:v>
       </x:c>
-      <x:c r="D7" s="6" t="str">
+      <x:c r="D9" s="6" t="str">
         <x:v>・技術再使用時にインスタントアクティベーションが可能</x:v>
       </x:c>
-      <x:c r="E7" s="6" t="str">
-        <x:v>・技術再使用時にインスタントアクティベーションが可能</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="30" customHeight="1">
-      <x:c r="A8" s="8" t="str"/>
-      <x:c r="B8" s="6" t="str">
+      <x:c r="E9" s="6" t="str">
+        <x:v>・スキル再使用時、即時発動可能</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" s="8"/>
+      <x:c r="B10" s="6" t="str">
         <x:v>・기술 사용 중 슈퍼 아머</x:v>
       </x:c>
-      <x:c r="C8" s="6" t="str">
+      <x:c r="C10" s="6" t="str">
         <x:v>・Super Armor during skill use</x:v>
       </x:c>
-      <x:c r="D8" s="6" t="str">
+      <x:c r="D10" s="6" t="str">
         <x:v>・技術使用時のスーパーアーマー</x:v>
       </x:c>
-      <x:c r="E8" s="6" t="str">
-        <x:v>・技術使用時のスーパーアーマー</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="30" customHeight="1">
-      <x:c r="A9" s="8" t="str"/>
-      <x:c r="B9" s="6" t="str">
+      <x:c r="E10" s="6" t="str">
+        <x:v>・スキル使用中、スーパーアーマー</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11" s="8"/>
+      <x:c r="B11" s="6" t="str">
         <x:v>・첫 타격 성공 시 기절</x:v>
       </x:c>
-      <x:c r="C9" s="6" t="str">
+      <x:c r="C11" s="6" t="str">
         <x:v>・Stun on first successful hit</x:v>
       </x:c>
-      <x:c r="D9" s="6" t="str">
+      <x:c r="D11" s="6" t="str">
         <x:v>・最初のヒット成功で気絶する</x:v>
       </x:c>
-      <x:c r="E9" s="6" t="str">
-        <x:v>・最初のヒット成功で気絶する</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="30" customHeight="1">
-      <x:c r="A10" s="8" t="str"/>
-      <x:c r="B10" s="6" t="str">
+      <x:c r="E11" s="6" t="str">
+        <x:v>・1回目の打撃成功時、気絶</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
+      <x:c r="A12" s="8"/>
+      <x:c r="B12" s="6" t="str">
         <x:v>・기술 재사용 시 기술 첫 사용 위치로 순간 이동</x:v>
       </x:c>
-      <x:c r="C10" s="6" t="str">
+      <x:c r="C12" s="6" t="str">
         <x:v>・Teleport to the first skill position when re-using skill</x:v>
       </x:c>
-      <x:c r="D10" s="6" t="str">
+      <x:c r="D12" s="6" t="str">
         <x:v>・技術を再使用するときに最初の技術位置にテレポートします</x:v>
       </x:c>
-      <x:c r="E10" s="6" t="str">
-        <x:v>・技術を再使用するときに最初の技術位置にテレポートします</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="30" customHeight="1">
-      <x:c r="A11" s="8" t="str"/>
-      <x:c r="B11" s="6" t="str">
+      <x:c r="E12" s="6" t="str">
+        <x:v>・スキル再使用時、スキル初使用位置に瞬間移動</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="15" hidden="0" customHeight="1">
+      <x:c r="A13"/>
+      <x:c r="B13" t="str">
         <x:v>・기술 재사용 중 슈퍼 아머 , 잡기 불가</x:v>
       </x:c>
-      <x:c r="C11" s="6" t="str">
+      <x:c r="C13" t="str">
         <x:v>・Super Armor , Grab Immunity while re-using skill</x:v>
       </x:c>
-      <x:c r="D11" s="6" t="str">
+      <x:c r="D13" t="str">
         <x:v>・スーパーアーマー、技術再使用中に免疫を獲得</x:v>
       </x:c>
-      <x:c r="E11" s="6" t="str">
-        <x:v>・スーパーアーマー、技術再使用中に免疫を獲得</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="30" customHeight="1">
-      <x:c r="A12" s="8" t="str"/>
-      <x:c r="B12" s="6" t="str">
+      <x:c r="E13" t="str">
+        <x:v>・スキル再使用中、スーパーアーマー、キャッチ不可</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="15" hidden="0" customHeight="1">
+      <x:c r="A14"/>
+      <x:c r="B14" t="str">
         <x:v>・타격한 대상에게 3 초 뒤 폭발하는 령부 부착</x:v>
       </x:c>
-      <x:c r="C12" s="6" t="str">
+      <x:c r="C14" t="str">
         <x:v>・Attaches a Talisman to the hit target that explodes after 3 seconds</x:v>
       </x:c>
-      <x:c r="D12" s="6" t="str">
+      <x:c r="D14" t="str">
         <x:v>・ヒットしたターゲットに護符を取り付け、3秒後に爆発します</x:v>
       </x:c>
-      <x:c r="E12" s="6" t="str">
-        <x:v>・ヒットしたターゲットに護符を取り付け、3秒後に爆発します</x:v>
+      <x:c r="E14" t="str">
+        <x:v>・打撃した対象に3秒後、爆発する霊符付着</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="15" hidden="0" customHeight="1">
+      <x:c r="A15"/>
+      <x:c r="B15"/>
+      <x:c r="C15"/>
+      <x:c r="D15"/>
+      <x:c r="E15" t="str">
+        <x:v>霊符爆発</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="15" hidden="0" customHeight="1">
+      <x:c r="A16"/>
+      <x:c r="B16"/>
+      <x:c r="C16"/>
+      <x:c r="D16"/>
+      <x:c r="E16" t="str">
+        <x:v>打撃ダメージ450%</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3532,7 +3749,7 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="4" t="str"/>
+      <x:c r="A1" s="4"/>
       <x:c r="B1" s="4" t="str">
         <x:v>韓国語</x:v>
       </x:c>
@@ -3560,7 +3777,7 @@
         <x:v>人中打ち</x:v>
       </x:c>
       <x:c r="E2" s="6" t="str">
-        <x:v>人中打ち</x:v>
+        <x:v>人中突き</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="30" customHeight="1">
@@ -3577,11 +3794,11 @@
         <x:v>PvP ｜系列 無欠 鮮明 かすかな</x:v>
       </x:c>
       <x:c r="E3" s="6" t="str">
-        <x:v>PvP ｜系列 無欠 鮮明 かすかな</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="30" customHeight="1">
-      <x:c r="A4" s="8" t="str"/>
+        <x:v>PvP</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="15" hidden="0" customHeight="1">
+      <x:c r="A4" s="8"/>
       <x:c r="B4" s="6" t="str">
         <x:v>"적의 틈을 노리고 순간적으로 돌진하여 찌른다."</x:v>
       </x:c>
@@ -3592,11 +3809,11 @@
         <x:v>敵の隙を狙って瞬時にダッシュして突き刺す。</x:v>
       </x:c>
       <x:c r="E4" s="6" t="str">
-        <x:v>敵の隙を狙って瞬時にダッシュして突き刺す。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="30" customHeight="1">
-      <x:c r="A5" s="8" t="str"/>
+        <x:v>敵の隙を狙って瞬時に近づいて突く。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="8"/>
       <x:c r="B5" s="6" t="str">
         <x:v>・최대 사용 횟수 : 2</x:v>
       </x:c>
@@ -3607,11 +3824,11 @@
         <x:v>・最大使用回数: 2</x:v>
       </x:c>
       <x:c r="E5" s="6" t="str">
-        <x:v>・最大使用回数: 2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="30" customHeight="1">
-      <x:c r="A6" s="8" t="str"/>
+        <x:v>最大使用回数：2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="8"/>
       <x:c r="B6" s="6" t="str">
         <x:v>・재사용 대기시간 : 6초</x:v>
       </x:c>
@@ -3622,52 +3839,70 @@
         <x:v>・再使用待機時間: 6秒</x:v>
       </x:c>
       <x:c r="E6" s="6" t="str">
-        <x:v>・再使用待機時間: 6秒</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="30" customHeight="1">
-      <x:c r="A7" s="8" t="str"/>
-      <x:c r="B7" s="6" t="str">
+        <x:v>再使用待機時間：6秒</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="8"/>
+      <x:c r="B7" s="6"/>
+      <x:c r="C7" s="6"/>
+      <x:c r="D7" s="6"/>
+      <x:c r="E7" s="6" t="str">
+        <x:v>・打撃ダメージ1412.63%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="8"/>
+      <x:c r="B8" s="6"/>
+      <x:c r="C8" s="6"/>
+      <x:c r="D8" s="6"/>
+      <x:c r="E8" s="6" t="str">
+        <x:v>・PVP打撃ダメージ706.32%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="8"/>
+      <x:c r="B9" s="6" t="str">
         <x:v>・기술 버튼 유지 시 최대 2 타격</x:v>
       </x:c>
-      <x:c r="C7" s="6" t="str">
+      <x:c r="C9" s="6" t="str">
         <x:v>・Max 2 hits when holding skill button</x:v>
       </x:c>
-      <x:c r="D7" s="6" t="str">
+      <x:c r="D9" s="6" t="str">
         <x:v>・技術ボタン押しっぱなしで最大2ヒット</x:v>
       </x:c>
-      <x:c r="E7" s="6" t="str">
-        <x:v>・技術ボタン押しっぱなしで最大2ヒット</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="30" customHeight="1">
-      <x:c r="A8" s="8" t="str"/>
-      <x:c r="B8" s="6" t="str">
+      <x:c r="E9" s="6" t="str">
+        <x:v>・スキルボタン長押しで最大2打撃</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10"/>
+      <x:c r="B10" t="str">
         <x:v>・기술 사용 중 슈퍼 아머</x:v>
       </x:c>
-      <x:c r="C8" s="6" t="str">
+      <x:c r="C10" t="str">
         <x:v>・Super Armor during skill use</x:v>
       </x:c>
-      <x:c r="D8" s="6" t="str">
+      <x:c r="D10" t="str">
         <x:v>・技術使用時のスーパーアーマー</x:v>
       </x:c>
-      <x:c r="E8" s="6" t="str">
-        <x:v>・技術使用時のスーパーアーマー</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="30" customHeight="1">
-      <x:c r="A9" s="8" t="str"/>
-      <x:c r="B9" s="6" t="str">
+      <x:c r="E10" t="str">
+        <x:v>・スキル使用中、スーパーアーマー</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11"/>
+      <x:c r="B11" t="str">
         <x:v>・타격 성공 시 기절</x:v>
       </x:c>
-      <x:c r="C9" s="6" t="str">
+      <x:c r="C11" t="str">
         <x:v>・Stun on successful hit</x:v>
       </x:c>
-      <x:c r="D9" s="6" t="str">
+      <x:c r="D11" t="str">
         <x:v>・ヒット成功時に気絶させる</x:v>
       </x:c>
-      <x:c r="E9" s="6" t="str">
-        <x:v>・ヒット成功時に気絶させる</x:v>
+      <x:c r="E11" t="str">
+        <x:v>・打撃成功時、気絶</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3687,7 +3922,7 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="4" t="str"/>
+      <x:c r="A1" s="4"/>
       <x:c r="B1" s="4" t="str">
         <x:v>韓国語</x:v>
       </x:c>
@@ -3715,7 +3950,7 @@
         <x:v>呪術：妖花乱</x:v>
       </x:c>
       <x:c r="E2" s="6" t="str">
-        <x:v>呪術：妖花乱</x:v>
+        <x:v>呪術：妖花蘭</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="30" customHeight="1">
@@ -3732,11 +3967,11 @@
         <x:v>PvE PvP ｜系列 無欠 鮮明 洗練された</x:v>
       </x:c>
       <x:c r="E3" s="6" t="str">
-        <x:v>PvE PvP ｜系列 無欠 鮮明 洗練された</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="30" customHeight="1">
-      <x:c r="A4" s="8" t="str"/>
+        <x:v>PvE PvP</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="15" hidden="0" customHeight="1">
+      <x:c r="A4" s="8"/>
       <x:c r="B4" s="6" t="str">
         <x:v>"주력을 해방하여 적을 공격한다."</x:v>
       </x:c>
@@ -3747,11 +3982,11 @@
         <x:v>「呪力を解放して敵を攻撃する。」</x:v>
       </x:c>
       <x:c r="E4" s="6" t="str">
-        <x:v>「呪力を解放して敵を攻撃する。」</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="30" customHeight="1">
-      <x:c r="A5" s="8" t="str"/>
+        <x:v>呪力を解放して敵を攻撃する。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="8"/>
       <x:c r="B5" s="6" t="str">
         <x:v>・최대 사용 횟수 : 1</x:v>
       </x:c>
@@ -3762,11 +3997,11 @@
         <x:v>・最大使用回数: 1</x:v>
       </x:c>
       <x:c r="E5" s="6" t="str">
-        <x:v>・最大使用回数: 1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="30" customHeight="1">
-      <x:c r="A6" s="8" t="str"/>
+        <x:v>最大使用回数：1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="8"/>
       <x:c r="B6" s="6" t="str">
         <x:v>・재사용 대기시간 : 6초</x:v>
       </x:c>
@@ -3777,82 +4012,136 @@
         <x:v>・再使用待機時間: 6秒</x:v>
       </x:c>
       <x:c r="E6" s="6" t="str">
-        <x:v>・再使用待機時間: 6秒</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="30" customHeight="1">
-      <x:c r="A7" s="8" t="str"/>
-      <x:c r="B7" s="6" t="str">
+        <x:v>再使用待機時間：6秒</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="8"/>
+      <x:c r="B7" s="6"/>
+      <x:c r="C7" s="6"/>
+      <x:c r="D7" s="6"/>
+      <x:c r="E7" s="6" t="str">
+        <x:v>・打撃ダメージ848.86%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="8"/>
+      <x:c r="B8" s="6"/>
+      <x:c r="C8" s="6"/>
+      <x:c r="D8" s="6"/>
+      <x:c r="E8" s="6" t="str">
+        <x:v>・PVP打撃ダメージ424.43%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="8"/>
+      <x:c r="B9" s="6" t="str">
         <x:v>・최대 5 타격</x:v>
       </x:c>
-      <x:c r="C7" s="6" t="str">
+      <x:c r="C9" s="6" t="str">
         <x:v>・Max 5 hits</x:v>
       </x:c>
-      <x:c r="D7" s="6" t="str">
+      <x:c r="D9" s="6" t="str">
         <x:v>・最大5ヒット</x:v>
       </x:c>
-      <x:c r="E7" s="6" t="str">
-        <x:v>・最大5ヒット</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="30" customHeight="1">
-      <x:c r="A8" s="8" t="str"/>
-      <x:c r="B8" s="6" t="str">
+      <x:c r="E9" s="6" t="str">
+        <x:v>・最大5打撃</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" s="8"/>
+      <x:c r="B10" s="6" t="str">
         <x:v>・기술 사용 중 슈퍼 아머</x:v>
       </x:c>
-      <x:c r="C8" s="6" t="str">
+      <x:c r="C10" s="6" t="str">
         <x:v>・Super Armor during skill use</x:v>
       </x:c>
-      <x:c r="D8" s="6" t="str">
+      <x:c r="D10" s="6" t="str">
         <x:v>・技術使用時のスーパーアーマー</x:v>
       </x:c>
-      <x:c r="E8" s="6" t="str">
-        <x:v>・技術使用時のスーパーアーマー</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="30" customHeight="1">
-      <x:c r="A9" s="8" t="str"/>
-      <x:c r="B9" s="6" t="str">
+      <x:c r="E10" s="6" t="str">
+        <x:v>・スキル使用中、スーパーアーマー</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11" s="8"/>
+      <x:c r="B11" s="6" t="str">
         <x:v>・마지막 타격 성공 시 넉다운</x:v>
       </x:c>
-      <x:c r="C9" s="6" t="str">
+      <x:c r="C11" s="6" t="str">
         <x:v>・Knockdown on last successful hit</x:v>
       </x:c>
-      <x:c r="D9" s="6" t="str">
+      <x:c r="D11" s="6" t="str">
         <x:v>・最後に成功したヒットでノックダウン</x:v>
       </x:c>
-      <x:c r="E9" s="6" t="str">
-        <x:v>・最後に成功したヒットでノックダウン</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="30" customHeight="1">
-      <x:c r="A10" s="8" t="str"/>
-      <x:c r="B10" s="6" t="str">
+      <x:c r="E11" s="6" t="str">
+        <x:v>・最後の打撃成功時、ノックダウン</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
+      <x:c r="A12"/>
+      <x:c r="B12" t="str">
         <x:v>・이동 공격 가능</x:v>
       </x:c>
-      <x:c r="C10" s="6" t="str">
+      <x:c r="C12" t="str">
         <x:v>・Possible to move while attacking</x:v>
       </x:c>
-      <x:c r="D10" s="6" t="str">
+      <x:c r="D12" t="str">
         <x:v>・攻撃しながら移動可能</x:v>
       </x:c>
-      <x:c r="E10" s="6" t="str">
-        <x:v>・攻撃しながら移動可能</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="30" customHeight="1">
-      <x:c r="A11" s="8" t="str"/>
-      <x:c r="B11" s="6" t="str">
+      <x:c r="E12" t="str">
+        <x:v>・移動攻撃可能</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="15" hidden="0" customHeight="1">
+      <x:c r="A13"/>
+      <x:c r="B13" t="str">
         <x:v>・기술 사용 시 역류 생성</x:v>
       </x:c>
-      <x:c r="C11" s="6" t="str">
+      <x:c r="C13" t="str">
         <x:v>・Creates Countercurrent when using skill</x:v>
       </x:c>
-      <x:c r="D11" s="6" t="str">
+      <x:c r="D13" t="str">
         <x:v>・技術使用時に逆流を発生させる</x:v>
       </x:c>
-      <x:c r="E11" s="6" t="str">
-        <x:v>・技術使用時に逆流を発生させる</x:v>
+      <x:c r="E13" t="str">
+        <x:v>・スキル使用時、逆流生成</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="15" hidden="0" customHeight="1">
+      <x:c r="A14"/>
+      <x:c r="B14"/>
+      <x:c r="C14"/>
+      <x:c r="D14"/>
+      <x:c r="E14" t="str">
+        <x:v>逆流</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="15" hidden="0" customHeight="1">
+      <x:c r="A15"/>
+      <x:c r="B15"/>
+      <x:c r="C15"/>
+      <x:c r="D15"/>
+      <x:c r="E15" t="str">
+        <x:v>打撃ダメージ848.86%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="15" hidden="0" customHeight="1">
+      <x:c r="A16"/>
+      <x:c r="B16"/>
+      <x:c r="C16"/>
+      <x:c r="D16"/>
+      <x:c r="E16" t="str">
+        <x:v>PVP打撃ダメージ424.43%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="15" hidden="0" customHeight="1">
+      <x:c r="A17"/>
+      <x:c r="B17"/>
+      <x:c r="C17"/>
+      <x:c r="D17"/>
+      <x:c r="E17" t="str">
+        <x:v>最大4打撃</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3872,7 +4161,7 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="4" t="str"/>
+      <x:c r="A1" s="4"/>
       <x:c r="B1" s="4" t="str">
         <x:v>韓国語</x:v>
       </x:c>
@@ -3900,7 +4189,7 @@
         <x:v>回転打ち</x:v>
       </x:c>
       <x:c r="E2" s="6" t="str">
-        <x:v>回転打ち</x:v>
+        <x:v>周舞</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="30" customHeight="1">
@@ -3917,11 +4206,11 @@
         <x:v>PvE PvP ｜系列 燦爛 鮮明 洗練された</x:v>
       </x:c>
       <x:c r="E3" s="6" t="str">
-        <x:v>PvE PvP ｜系列 燦爛 鮮明 洗練された</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="30" customHeight="1">
-      <x:c r="A4" s="8" t="str"/>
+        <x:v>PvE PvP</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="15" hidden="0" customHeight="1">
+      <x:c r="A4" s="8"/>
       <x:c r="B4" s="6" t="str">
         <x:v>"춤을 추듯 회전하며 적의 측면을 파고든다."</x:v>
       </x:c>
@@ -3932,11 +4221,11 @@
         <x:v>「優雅に舞うように回転しながら敵の側面を貫く。」</x:v>
       </x:c>
       <x:c r="E4" s="6" t="str">
-        <x:v>「優雅に舞うように回転しながら敵の側面を貫く。」</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="30" customHeight="1">
-      <x:c r="A5" s="8" t="str"/>
+        <x:v>舞うように敵の側面に移動しながら、招画扇で攻撃する。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="8"/>
       <x:c r="B5" s="6" t="str">
         <x:v>・최대 사용 횟수 : 3</x:v>
       </x:c>
@@ -3947,11 +4236,11 @@
         <x:v>・最大使用回数: 3</x:v>
       </x:c>
       <x:c r="E5" s="6" t="str">
-        <x:v>・最大使用回数: 3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="30" customHeight="1">
-      <x:c r="A6" s="8" t="str"/>
+        <x:v>最大使用回数：3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="8"/>
       <x:c r="B6" s="6" t="str">
         <x:v>・재사용 대기시간 : 5초</x:v>
       </x:c>
@@ -3962,67 +4251,85 @@
         <x:v>・再使用待機時間: 5秒</x:v>
       </x:c>
       <x:c r="E6" s="6" t="str">
-        <x:v>・再使用待機時間: 5秒</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="30" customHeight="1">
-      <x:c r="A7" s="8" t="str"/>
-      <x:c r="B7" s="6" t="str">
+        <x:v>再使用待機時間：5秒</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="8"/>
+      <x:c r="B7" s="6"/>
+      <x:c r="C7" s="6"/>
+      <x:c r="D7" s="6"/>
+      <x:c r="E7" s="6" t="str">
+        <x:v>・打撃ダメージ734.57%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="8"/>
+      <x:c r="B8" s="6"/>
+      <x:c r="C8" s="6"/>
+      <x:c r="D8" s="6"/>
+      <x:c r="E8" s="6" t="str">
+        <x:v>・PVP打撃ダメージ367.27%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="8"/>
+      <x:c r="B9" s="6" t="str">
         <x:v>・최대 3 타격</x:v>
       </x:c>
-      <x:c r="C7" s="6" t="str">
+      <x:c r="C9" s="6" t="str">
         <x:v>・Max 3 hits</x:v>
       </x:c>
-      <x:c r="D7" s="6" t="str">
+      <x:c r="D9" s="6" t="str">
         <x:v>・最大3ヒット</x:v>
       </x:c>
-      <x:c r="E7" s="6" t="str">
-        <x:v>・最大3ヒット</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="30" customHeight="1">
-      <x:c r="A8" s="8" t="str"/>
-      <x:c r="B8" s="6" t="str">
+      <x:c r="E9" s="6" t="str">
+        <x:v>・最大3打撃</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A10" s="8"/>
+      <x:c r="B10" s="6" t="str">
         <x:v>・기술 버튼 유지 시 정신력 30 을 소모하여 3 회 추가 타격</x:v>
       </x:c>
-      <x:c r="C8" s="6" t="str">
+      <x:c r="C10" s="6" t="str">
         <x:v>・Consumes 30 MP to perform 3 additional hits when holding skill button</x:v>
       </x:c>
-      <x:c r="D8" s="6" t="str">
+      <x:c r="D10" s="6" t="str">
         <x:v>・技術ボタン長押しで30精神力を消費して追加で3回ヒットする</x:v>
       </x:c>
-      <x:c r="E8" s="6" t="str">
-        <x:v>・技術ボタン長押しで30精神力を消費して追加で3回ヒットする</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="30" customHeight="1">
-      <x:c r="A9" s="8" t="str"/>
-      <x:c r="B9" s="6" t="str">
+      <x:c r="E10" s="6" t="str">
+        <x:v>・スキルボタン長押しでMPを30消費して3回追加使用</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11"/>
+      <x:c r="B11" t="str">
         <x:v>・기술 사용 중 슈퍼 아머</x:v>
       </x:c>
-      <x:c r="C9" s="6" t="str">
+      <x:c r="C11" t="str">
         <x:v>・Super Armor during skill use</x:v>
       </x:c>
-      <x:c r="D9" s="6" t="str">
+      <x:c r="D11" t="str">
         <x:v>・技術使用時のスーパーアーマー</x:v>
       </x:c>
-      <x:c r="E9" s="6" t="str">
-        <x:v>・技術使用時のスーパーアーマー</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="30" customHeight="1">
-      <x:c r="A10" s="8" t="str"/>
-      <x:c r="B10" s="6" t="str">
+      <x:c r="E11" t="str">
+        <x:v>・スキル使用中、スーパーアーマー</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
+      <x:c r="A12"/>
+      <x:c r="B12" t="str">
         <x:v>・첫 타격 성공 시 띄우기</x:v>
       </x:c>
-      <x:c r="C10" s="6" t="str">
+      <x:c r="C12" t="str">
         <x:v>・Knock-up on first successful hit</x:v>
       </x:c>
-      <x:c r="D10" s="6" t="str">
+      <x:c r="D12" t="str">
         <x:v>・最初のヒット成功で浮かせ</x:v>
       </x:c>
-      <x:c r="E10" s="6" t="str">
-        <x:v>・最初のヒット成功で浮かせ</x:v>
+      <x:c r="E12" t="str">
+        <x:v>・1回目の打撃成功時、浮かす</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4042,7 +4349,7 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="4" t="str"/>
+      <x:c r="A1" s="4"/>
       <x:c r="B1" s="4" t="str">
         <x:v>韓国語</x:v>
       </x:c>
@@ -4087,11 +4394,11 @@
         <x:v>PvE PvP ｜系列 無欠 鮮明 洗練された</x:v>
       </x:c>
       <x:c r="E3" s="6" t="str">
-        <x:v>PvE PvP ｜系列 無欠 鮮明 洗練された</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="30" customHeight="1">
-      <x:c r="A4" s="8" t="str"/>
+        <x:v>PvE PvP</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="15" hidden="0" customHeight="1">
+      <x:c r="A4" s="8"/>
       <x:c r="B4" s="6" t="str">
         <x:v>"주력으로 상대를 결박하여 공격한다."</x:v>
       </x:c>
@@ -4102,11 +4409,11 @@
         <x:v>相手を呪力で拘束して攻撃する。</x:v>
       </x:c>
       <x:c r="E4" s="6" t="str">
-        <x:v>相手を呪力で拘束して攻撃する。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="30" customHeight="1">
-      <x:c r="A5" s="8" t="str"/>
+        <x:v>呪力で相手を縛り付けて攻撃する。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="8"/>
       <x:c r="B5" s="6" t="str">
         <x:v>・최대 사용 횟수 : 1</x:v>
       </x:c>
@@ -4117,11 +4424,11 @@
         <x:v>・最大使用回数: 1</x:v>
       </x:c>
       <x:c r="E5" s="6" t="str">
-        <x:v>・最大使用回数: 1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="30" customHeight="1">
-      <x:c r="A6" s="8" t="str"/>
+        <x:v>最大使用回数：1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="8"/>
       <x:c r="B6" s="6" t="str">
         <x:v>・재사용 대기시간 : 6초</x:v>
       </x:c>
@@ -4132,52 +4439,106 @@
         <x:v>・再使用待機時間: 6秒</x:v>
       </x:c>
       <x:c r="E6" s="6" t="str">
-        <x:v>・再使用待機時間: 6秒</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="30" customHeight="1">
-      <x:c r="A7" s="8" t="str"/>
-      <x:c r="B7" s="6" t="str">
+        <x:v>再使用待機時間：6秒</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="8"/>
+      <x:c r="B7" s="6"/>
+      <x:c r="C7" s="6"/>
+      <x:c r="D7" s="6"/>
+      <x:c r="E7" s="6" t="str">
+        <x:v>・打撃ダメージ1195.6%x3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="8"/>
+      <x:c r="B8" s="6"/>
+      <x:c r="C8" s="6"/>
+      <x:c r="D8" s="6"/>
+      <x:c r="E8" s="6" t="str">
+        <x:v>・PVP打撃ダメージ597.8%x3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="8"/>
+      <x:c r="B9" s="6" t="str">
         <x:v>・기술 사용 중 슈퍼 아머</x:v>
       </x:c>
-      <x:c r="C7" s="6" t="str">
+      <x:c r="C9" s="6" t="str">
         <x:v>・Super Armor during skill use</x:v>
       </x:c>
-      <x:c r="D7" s="6" t="str">
+      <x:c r="D9" s="6" t="str">
         <x:v>・技術使用時のスーパーアーマー</x:v>
       </x:c>
-      <x:c r="E7" s="6" t="str">
-        <x:v>・技術使用時のスーパーアーマー</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="30" customHeight="1">
-      <x:c r="A8" s="8" t="str"/>
-      <x:c r="B8" s="6" t="str">
+      <x:c r="E9" s="6" t="str">
+        <x:v>・スキル使用中、スーパーアーマー</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" s="5"/>
+      <x:c r="B10" s="5" t="str">
         <x:v>・타격 성공 시 넉다운</x:v>
       </x:c>
-      <x:c r="C8" s="6" t="str">
+      <x:c r="C10" s="5" t="str">
         <x:v>・Knockdown on successful hit</x:v>
       </x:c>
-      <x:c r="D8" s="6" t="str">
+      <x:c r="D10" s="5" t="str">
         <x:v>・ヒット成功時のノックダウン</x:v>
       </x:c>
-      <x:c r="E8" s="6" t="str">
-        <x:v>・ヒット成功時のノックダウン</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="30" customHeight="1">
-      <x:c r="A9" s="8" t="str"/>
-      <x:c r="B9" s="6" t="str">
+      <x:c r="E10" s="5" t="str">
+        <x:v>・打撃成功時、ノックダウン</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11" s="5"/>
+      <x:c r="B11" s="5" t="str">
         <x:v>・기술 사용 시 주박 생성</x:v>
       </x:c>
-      <x:c r="C9" s="6" t="str">
+      <x:c r="C11" s="5" t="str">
         <x:v>・Creates Mystic Binding when using skill</x:v>
       </x:c>
-      <x:c r="D9" s="6" t="str">
+      <x:c r="D11" s="5" t="str">
         <x:v>・技術使用時にミスティックバインドを発生させる</x:v>
       </x:c>
-      <x:c r="E9" s="6" t="str">
-        <x:v>・技術使用時にミスティックバインドを発生させる</x:v>
+      <x:c r="E11" s="5" t="str">
+        <x:v>・スキル使用時、呪縛生成</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
+      <x:c r="A12" s="5"/>
+      <x:c r="B12" s="5"/>
+      <x:c r="C12" s="5"/>
+      <x:c r="D12" s="5"/>
+      <x:c r="E12" s="5" t="str">
+        <x:v>呪縛</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="15" hidden="0" customHeight="1">
+      <x:c r="A13" s="5"/>
+      <x:c r="B13" s="5"/>
+      <x:c r="C13" s="5"/>
+      <x:c r="D13" s="5"/>
+      <x:c r="E13" s="5" t="str">
+        <x:v>打撃ダメージ1195.6%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="15" hidden="0" customHeight="1">
+      <x:c r="A14" s="5"/>
+      <x:c r="B14" s="5"/>
+      <x:c r="C14" s="5"/>
+      <x:c r="D14" s="5"/>
+      <x:c r="E14" s="5" t="str">
+        <x:v>PVP打撃ダメージ418.46%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="15" hidden="0" customHeight="1">
+      <x:c r="A15" s="5"/>
+      <x:c r="B15" s="5"/>
+      <x:c r="C15" s="5"/>
+      <x:c r="D15" s="5"/>
+      <x:c r="E15" s="5" t="str">
+        <x:v>最大4打撃</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4197,7 +4558,7 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="4" t="str"/>
+      <x:c r="A1" s="4"/>
       <x:c r="B1" s="4" t="str">
         <x:v>韓国語</x:v>
       </x:c>
@@ -4225,7 +4586,7 @@
         <x:v>前足裂き</x:v>
       </x:c>
       <x:c r="E2" s="6" t="str">
-        <x:v>前足裂き</x:v>
+        <x:v>掬い斬り</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="30" customHeight="1">
@@ -4242,11 +4603,11 @@
         <x:v>PvE ｜系列 守護 鮮明 洗練された</x:v>
       </x:c>
       <x:c r="E3" s="6" t="str">
-        <x:v>PvE ｜系列 守護 鮮明 洗練された</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="30" customHeight="1">
-      <x:c r="A4" s="8" t="str"/>
+        <x:v>PvE</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="15" hidden="0" customHeight="1">
+      <x:c r="A4" s="8"/>
       <x:c r="B4" s="6" t="str">
         <x:v>"여우 신령의 발톱 형상을 빌려와 올려 벤다."</x:v>
       </x:c>
@@ -4257,11 +4618,11 @@
         <x:v>「狐の精の爪の形を借りて上に斬り上げる。」</x:v>
       </x:c>
       <x:c r="E4" s="6" t="str">
-        <x:v>「狐の精の爪の形を借りて上に斬り上げる。」</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="30" customHeight="1">
-      <x:c r="A5" s="8" t="str"/>
+        <x:v>狐神霊の爪の形状を用いて敵を斬り上げる。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="8"/>
       <x:c r="B5" s="6" t="str">
         <x:v>・최대 사용 횟수 : 2</x:v>
       </x:c>
@@ -4272,11 +4633,11 @@
         <x:v>・最大使用回数: 2</x:v>
       </x:c>
       <x:c r="E5" s="6" t="str">
-        <x:v>・最大使用回数: 2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="30" customHeight="1">
-      <x:c r="A6" s="8" t="str"/>
+        <x:v>最大使用回数：2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="8"/>
       <x:c r="B6" s="6" t="str">
         <x:v>・재사용 대기시간 : 6초</x:v>
       </x:c>
@@ -4287,67 +4648,85 @@
         <x:v>・再使用待機時間: 6秒</x:v>
       </x:c>
       <x:c r="E6" s="6" t="str">
-        <x:v>・再使用待機時間: 6秒</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="30" customHeight="1">
-      <x:c r="A7" s="8" t="str"/>
-      <x:c r="B7" s="6" t="str">
+        <x:v>再使用待機時間：6秒</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="8"/>
+      <x:c r="B7" s="6"/>
+      <x:c r="C7" s="6"/>
+      <x:c r="D7" s="6"/>
+      <x:c r="E7" s="6" t="str">
+        <x:v>・打撃ダメージ1150.65%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="8"/>
+      <x:c r="B8" s="6"/>
+      <x:c r="C8" s="6"/>
+      <x:c r="D8" s="6"/>
+      <x:c r="E8" s="6" t="str">
+        <x:v>・PVP打撃ダメージ575.33%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="8"/>
+      <x:c r="B9" s="6" t="str">
         <x:v>・기술 버튼 유지 시 최대 4 타격</x:v>
       </x:c>
-      <x:c r="C7" s="6" t="str">
+      <x:c r="C9" s="6" t="str">
         <x:v>・Max 4 hits when holding skill button</x:v>
       </x:c>
-      <x:c r="D7" s="6" t="str">
+      <x:c r="D9" s="6" t="str">
         <x:v>・技術ボタン押しっぱなしで最大4ヒット</x:v>
       </x:c>
-      <x:c r="E7" s="6" t="str">
-        <x:v>・技術ボタン押しっぱなしで最大4ヒット</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="30" customHeight="1">
-      <x:c r="A8" s="8" t="str"/>
-      <x:c r="B8" s="6" t="str">
+      <x:c r="E9" s="6" t="str">
+        <x:v>・スキルボタン長押しで最大4打撃</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" s="8"/>
+      <x:c r="B10" s="6" t="str">
         <x:v>・기술 사용 중 슈퍼 아머</x:v>
       </x:c>
-      <x:c r="C8" s="6" t="str">
+      <x:c r="C10" s="6" t="str">
         <x:v>・Super Armor during skill use</x:v>
       </x:c>
-      <x:c r="D8" s="6" t="str">
+      <x:c r="D10" s="6" t="str">
         <x:v>・技術使用時のスーパーアーマー</x:v>
       </x:c>
-      <x:c r="E8" s="6" t="str">
-        <x:v>・技術使用時のスーパーアーマー</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="30" customHeight="1">
-      <x:c r="A9" s="8" t="str"/>
-      <x:c r="B9" s="6" t="str">
+      <x:c r="E10" s="6" t="str">
+        <x:v>・スキル使用中、スーパーアーマー</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11" s="5"/>
+      <x:c r="B11" s="5" t="str">
         <x:v>・첫 타격 성공 시 경직</x:v>
       </x:c>
-      <x:c r="C9" s="6" t="str">
+      <x:c r="C11" s="5" t="str">
         <x:v>・Stiffness on first successful hit</x:v>
       </x:c>
-      <x:c r="D9" s="6" t="str">
+      <x:c r="D11" s="5" t="str">
         <x:v>・最初の成功時の硬さ</x:v>
       </x:c>
-      <x:c r="E9" s="6" t="str">
-        <x:v>・最初の成功時の硬さ</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="30" customHeight="1">
-      <x:c r="A10" s="8" t="str"/>
-      <x:c r="B10" s="6" t="str">
+      <x:c r="E11" s="5" t="str">
+        <x:v>・1回目の打撃成功時、硬直</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
+      <x:c r="A12" s="5"/>
+      <x:c r="B12" s="5" t="str">
         <x:v>・마지막 타격 성공 시 넉백</x:v>
       </x:c>
-      <x:c r="C10" s="6" t="str">
+      <x:c r="C12" s="5" t="str">
         <x:v>・Knockback on last successful hit</x:v>
       </x:c>
-      <x:c r="D10" s="6" t="str">
+      <x:c r="D12" s="5" t="str">
         <x:v>・最後に成功したヒットでノックバック</x:v>
       </x:c>
-      <x:c r="E10" s="6" t="str">
-        <x:v>・最後に成功したヒットでノックバック</x:v>
+      <x:c r="E12" s="5" t="str">
+        <x:v>・最後の打撃成功時、ノックバック</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
